--- a/sheets/rumman-calculator-template.xlsx
+++ b/sheets/rumman-calculator-template.xlsx
@@ -41406,9 +41406,12 @@
     <cfRule type="cellIs" priority="2" operator="equal" dxfId="6">
       <formula>"غير مكتمل"</formula>
     </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="8">
+      <formula>"محذوف"</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:L303">
-    <cfRule type="expression" priority="3" dxfId="2">
+    <cfRule type="expression" priority="4" dxfId="2">
       <formula>AND(MOD(ROW(),2)=1,$A4&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -41417,7 +41420,7 @@
       <formula1>"قطعة,رزمة,لفة,رول,كرتونة,كغ"</formula1>
     </dataValidation>
     <dataValidation sqref="I4:I303" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="قيمة غير صحيحة" error="اختر قيمة من القائمة." type="list">
-      <formula1>"مكتمل,غير مكتمل"</formula1>
+      <formula1>"مكتمل,غير مكتمل,محذوف"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/sheets/rumman-calculator-template.xlsx
+++ b/sheets/rumman-calculator-template.xlsx
@@ -20,9 +20,9 @@
     <sheet name="سجل التعديلات" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'البرادات'!$A$3:$W$303</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'البرادات'!$A$3:$X$303</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'البرادات'!$3:$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'المزارعون'!$A$3:$J$303</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'المزارعون'!$A$3:$K$303</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'المزارعون'!$3:$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'مشتريات الرمان'!$A$3:$Z$303</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'مشتريات الرمان'!$3:$3</definedName>
@@ -10107,7 +10107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W303"/>
+  <dimension ref="A1:X303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -10133,6 +10133,7 @@
     <col width="20" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
     <col hidden="1" width="12" customWidth="1" min="23" max="23"/>
+    <col hidden="1" width="15" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="44" customHeight="1">
@@ -10163,11 +10164,12 @@
       <c r="U1" s="32" t="n"/>
       <c r="V1" s="32" t="n"/>
       <c r="W1" s="32" t="n"/>
+      <c r="X1" s="32" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>بيانات كل براد وحالته. أعمدة «عند التقفيل» تُحفظ مرة واحدة لحظة التقفيل ولا تتغير بعدها.</t>
+          <t>بيانات كل براد وحالته. أعمدة «عند التقفيل» تُحفظ لحظة التقفيل ولا تغيّرها إعادة الفتح؛ إن أُعيد تقفيل البراد تُستبدل بأرقام التقفيل الأخير، والأرقام السابقة محفوظة في «سجل التعديلات».</t>
         </is>
       </c>
       <c r="B2" s="33" t="n"/>
@@ -10192,6 +10194,7 @@
       <c r="U2" s="33" t="n"/>
       <c r="V2" s="33" t="n"/>
       <c r="W2" s="33" t="n"/>
+      <c r="X2" s="33" t="n"/>
     </row>
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
@@ -10307,6 +10310,11 @@
       <c r="W3" s="35" t="inlineStr">
         <is>
           <t>الإصدار</t>
+        </is>
+      </c>
+      <c r="X3" s="34" t="inlineStr">
+        <is>
+          <t>مفتاح عدم التكرار</t>
         </is>
       </c>
     </row>
@@ -10334,6 +10342,7 @@
       <c r="U4" s="39" t="n"/>
       <c r="V4" s="38" t="n"/>
       <c r="W4" s="37" t="n"/>
+      <c r="X4" s="36" t="n"/>
     </row>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="36" t="n"/>
@@ -10359,6 +10368,7 @@
       <c r="U5" s="39" t="n"/>
       <c r="V5" s="38" t="n"/>
       <c r="W5" s="37" t="n"/>
+      <c r="X5" s="36" t="n"/>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="36" t="n"/>
@@ -10384,6 +10394,7 @@
       <c r="U6" s="39" t="n"/>
       <c r="V6" s="38" t="n"/>
       <c r="W6" s="37" t="n"/>
+      <c r="X6" s="36" t="n"/>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="36" t="n"/>
@@ -10409,6 +10420,7 @@
       <c r="U7" s="39" t="n"/>
       <c r="V7" s="38" t="n"/>
       <c r="W7" s="37" t="n"/>
+      <c r="X7" s="36" t="n"/>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="36" t="n"/>
@@ -10434,6 +10446,7 @@
       <c r="U8" s="39" t="n"/>
       <c r="V8" s="38" t="n"/>
       <c r="W8" s="37" t="n"/>
+      <c r="X8" s="36" t="n"/>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="36" t="n"/>
@@ -10459,6 +10472,7 @@
       <c r="U9" s="39" t="n"/>
       <c r="V9" s="38" t="n"/>
       <c r="W9" s="37" t="n"/>
+      <c r="X9" s="36" t="n"/>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="36" t="n"/>
@@ -10484,6 +10498,7 @@
       <c r="U10" s="39" t="n"/>
       <c r="V10" s="38" t="n"/>
       <c r="W10" s="37" t="n"/>
+      <c r="X10" s="36" t="n"/>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="36" t="n"/>
@@ -10509,6 +10524,7 @@
       <c r="U11" s="39" t="n"/>
       <c r="V11" s="38" t="n"/>
       <c r="W11" s="37" t="n"/>
+      <c r="X11" s="36" t="n"/>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="36" t="n"/>
@@ -10534,6 +10550,7 @@
       <c r="U12" s="39" t="n"/>
       <c r="V12" s="38" t="n"/>
       <c r="W12" s="37" t="n"/>
+      <c r="X12" s="36" t="n"/>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="36" t="n"/>
@@ -10559,6 +10576,7 @@
       <c r="U13" s="39" t="n"/>
       <c r="V13" s="38" t="n"/>
       <c r="W13" s="37" t="n"/>
+      <c r="X13" s="36" t="n"/>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="36" t="n"/>
@@ -10584,6 +10602,7 @@
       <c r="U14" s="39" t="n"/>
       <c r="V14" s="38" t="n"/>
       <c r="W14" s="37" t="n"/>
+      <c r="X14" s="36" t="n"/>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="36" t="n"/>
@@ -10609,6 +10628,7 @@
       <c r="U15" s="39" t="n"/>
       <c r="V15" s="38" t="n"/>
       <c r="W15" s="37" t="n"/>
+      <c r="X15" s="36" t="n"/>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="36" t="n"/>
@@ -10634,6 +10654,7 @@
       <c r="U16" s="39" t="n"/>
       <c r="V16" s="38" t="n"/>
       <c r="W16" s="37" t="n"/>
+      <c r="X16" s="36" t="n"/>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="36" t="n"/>
@@ -10659,6 +10680,7 @@
       <c r="U17" s="39" t="n"/>
       <c r="V17" s="38" t="n"/>
       <c r="W17" s="37" t="n"/>
+      <c r="X17" s="36" t="n"/>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="36" t="n"/>
@@ -10684,6 +10706,7 @@
       <c r="U18" s="39" t="n"/>
       <c r="V18" s="38" t="n"/>
       <c r="W18" s="37" t="n"/>
+      <c r="X18" s="36" t="n"/>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="36" t="n"/>
@@ -10709,6 +10732,7 @@
       <c r="U19" s="39" t="n"/>
       <c r="V19" s="38" t="n"/>
       <c r="W19" s="37" t="n"/>
+      <c r="X19" s="36" t="n"/>
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="36" t="n"/>
@@ -10734,6 +10758,7 @@
       <c r="U20" s="39" t="n"/>
       <c r="V20" s="38" t="n"/>
       <c r="W20" s="37" t="n"/>
+      <c r="X20" s="36" t="n"/>
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="36" t="n"/>
@@ -10759,6 +10784,7 @@
       <c r="U21" s="39" t="n"/>
       <c r="V21" s="38" t="n"/>
       <c r="W21" s="37" t="n"/>
+      <c r="X21" s="36" t="n"/>
     </row>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="36" t="n"/>
@@ -10784,6 +10810,7 @@
       <c r="U22" s="39" t="n"/>
       <c r="V22" s="38" t="n"/>
       <c r="W22" s="37" t="n"/>
+      <c r="X22" s="36" t="n"/>
     </row>
     <row r="23" ht="28" customHeight="1">
       <c r="A23" s="36" t="n"/>
@@ -10809,6 +10836,7 @@
       <c r="U23" s="39" t="n"/>
       <c r="V23" s="38" t="n"/>
       <c r="W23" s="37" t="n"/>
+      <c r="X23" s="36" t="n"/>
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="36" t="n"/>
@@ -10834,6 +10862,7 @@
       <c r="U24" s="39" t="n"/>
       <c r="V24" s="38" t="n"/>
       <c r="W24" s="37" t="n"/>
+      <c r="X24" s="36" t="n"/>
     </row>
     <row r="25" ht="28" customHeight="1">
       <c r="A25" s="36" t="n"/>
@@ -10859,6 +10888,7 @@
       <c r="U25" s="39" t="n"/>
       <c r="V25" s="38" t="n"/>
       <c r="W25" s="37" t="n"/>
+      <c r="X25" s="36" t="n"/>
     </row>
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="36" t="n"/>
@@ -10884,6 +10914,7 @@
       <c r="U26" s="39" t="n"/>
       <c r="V26" s="38" t="n"/>
       <c r="W26" s="37" t="n"/>
+      <c r="X26" s="36" t="n"/>
     </row>
     <row r="27" ht="28" customHeight="1">
       <c r="A27" s="36" t="n"/>
@@ -10909,6 +10940,7 @@
       <c r="U27" s="39" t="n"/>
       <c r="V27" s="38" t="n"/>
       <c r="W27" s="37" t="n"/>
+      <c r="X27" s="36" t="n"/>
     </row>
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="36" t="n"/>
@@ -10934,6 +10966,7 @@
       <c r="U28" s="39" t="n"/>
       <c r="V28" s="38" t="n"/>
       <c r="W28" s="37" t="n"/>
+      <c r="X28" s="36" t="n"/>
     </row>
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="36" t="n"/>
@@ -10959,6 +10992,7 @@
       <c r="U29" s="39" t="n"/>
       <c r="V29" s="38" t="n"/>
       <c r="W29" s="37" t="n"/>
+      <c r="X29" s="36" t="n"/>
     </row>
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="36" t="n"/>
@@ -10984,6 +11018,7 @@
       <c r="U30" s="39" t="n"/>
       <c r="V30" s="38" t="n"/>
       <c r="W30" s="37" t="n"/>
+      <c r="X30" s="36" t="n"/>
     </row>
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="36" t="n"/>
@@ -11009,6 +11044,7 @@
       <c r="U31" s="39" t="n"/>
       <c r="V31" s="38" t="n"/>
       <c r="W31" s="37" t="n"/>
+      <c r="X31" s="36" t="n"/>
     </row>
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="36" t="n"/>
@@ -11034,6 +11070,7 @@
       <c r="U32" s="39" t="n"/>
       <c r="V32" s="38" t="n"/>
       <c r="W32" s="37" t="n"/>
+      <c r="X32" s="36" t="n"/>
     </row>
     <row r="33" ht="28" customHeight="1">
       <c r="A33" s="36" t="n"/>
@@ -11059,6 +11096,7 @@
       <c r="U33" s="39" t="n"/>
       <c r="V33" s="38" t="n"/>
       <c r="W33" s="37" t="n"/>
+      <c r="X33" s="36" t="n"/>
     </row>
     <row r="34" ht="28" customHeight="1">
       <c r="A34" s="36" t="n"/>
@@ -11084,6 +11122,7 @@
       <c r="U34" s="39" t="n"/>
       <c r="V34" s="38" t="n"/>
       <c r="W34" s="37" t="n"/>
+      <c r="X34" s="36" t="n"/>
     </row>
     <row r="35" ht="28" customHeight="1">
       <c r="A35" s="36" t="n"/>
@@ -11109,6 +11148,7 @@
       <c r="U35" s="39" t="n"/>
       <c r="V35" s="38" t="n"/>
       <c r="W35" s="37" t="n"/>
+      <c r="X35" s="36" t="n"/>
     </row>
     <row r="36" ht="28" customHeight="1">
       <c r="A36" s="36" t="n"/>
@@ -11134,6 +11174,7 @@
       <c r="U36" s="39" t="n"/>
       <c r="V36" s="38" t="n"/>
       <c r="W36" s="37" t="n"/>
+      <c r="X36" s="36" t="n"/>
     </row>
     <row r="37" ht="28" customHeight="1">
       <c r="A37" s="36" t="n"/>
@@ -11159,6 +11200,7 @@
       <c r="U37" s="39" t="n"/>
       <c r="V37" s="38" t="n"/>
       <c r="W37" s="37" t="n"/>
+      <c r="X37" s="36" t="n"/>
     </row>
     <row r="38" ht="28" customHeight="1">
       <c r="A38" s="36" t="n"/>
@@ -11184,6 +11226,7 @@
       <c r="U38" s="39" t="n"/>
       <c r="V38" s="38" t="n"/>
       <c r="W38" s="37" t="n"/>
+      <c r="X38" s="36" t="n"/>
     </row>
     <row r="39" ht="28" customHeight="1">
       <c r="A39" s="36" t="n"/>
@@ -11209,6 +11252,7 @@
       <c r="U39" s="39" t="n"/>
       <c r="V39" s="38" t="n"/>
       <c r="W39" s="37" t="n"/>
+      <c r="X39" s="36" t="n"/>
     </row>
     <row r="40" ht="28" customHeight="1">
       <c r="A40" s="36" t="n"/>
@@ -11234,6 +11278,7 @@
       <c r="U40" s="39" t="n"/>
       <c r="V40" s="38" t="n"/>
       <c r="W40" s="37" t="n"/>
+      <c r="X40" s="36" t="n"/>
     </row>
     <row r="41" ht="28" customHeight="1">
       <c r="A41" s="36" t="n"/>
@@ -11259,6 +11304,7 @@
       <c r="U41" s="39" t="n"/>
       <c r="V41" s="38" t="n"/>
       <c r="W41" s="37" t="n"/>
+      <c r="X41" s="36" t="n"/>
     </row>
     <row r="42" ht="28" customHeight="1">
       <c r="A42" s="36" t="n"/>
@@ -11284,6 +11330,7 @@
       <c r="U42" s="39" t="n"/>
       <c r="V42" s="38" t="n"/>
       <c r="W42" s="37" t="n"/>
+      <c r="X42" s="36" t="n"/>
     </row>
     <row r="43" ht="28" customHeight="1">
       <c r="A43" s="36" t="n"/>
@@ -11309,6 +11356,7 @@
       <c r="U43" s="39" t="n"/>
       <c r="V43" s="38" t="n"/>
       <c r="W43" s="37" t="n"/>
+      <c r="X43" s="36" t="n"/>
     </row>
     <row r="44" ht="28" customHeight="1">
       <c r="A44" s="36" t="n"/>
@@ -11334,6 +11382,7 @@
       <c r="U44" s="39" t="n"/>
       <c r="V44" s="38" t="n"/>
       <c r="W44" s="37" t="n"/>
+      <c r="X44" s="36" t="n"/>
     </row>
     <row r="45" ht="28" customHeight="1">
       <c r="A45" s="36" t="n"/>
@@ -11359,6 +11408,7 @@
       <c r="U45" s="39" t="n"/>
       <c r="V45" s="38" t="n"/>
       <c r="W45" s="37" t="n"/>
+      <c r="X45" s="36" t="n"/>
     </row>
     <row r="46" ht="28" customHeight="1">
       <c r="A46" s="36" t="n"/>
@@ -11384,6 +11434,7 @@
       <c r="U46" s="39" t="n"/>
       <c r="V46" s="38" t="n"/>
       <c r="W46" s="37" t="n"/>
+      <c r="X46" s="36" t="n"/>
     </row>
     <row r="47" ht="28" customHeight="1">
       <c r="A47" s="36" t="n"/>
@@ -11409,6 +11460,7 @@
       <c r="U47" s="39" t="n"/>
       <c r="V47" s="38" t="n"/>
       <c r="W47" s="37" t="n"/>
+      <c r="X47" s="36" t="n"/>
     </row>
     <row r="48" ht="28" customHeight="1">
       <c r="A48" s="36" t="n"/>
@@ -11434,6 +11486,7 @@
       <c r="U48" s="39" t="n"/>
       <c r="V48" s="38" t="n"/>
       <c r="W48" s="37" t="n"/>
+      <c r="X48" s="36" t="n"/>
     </row>
     <row r="49" ht="28" customHeight="1">
       <c r="A49" s="36" t="n"/>
@@ -11459,6 +11512,7 @@
       <c r="U49" s="39" t="n"/>
       <c r="V49" s="38" t="n"/>
       <c r="W49" s="37" t="n"/>
+      <c r="X49" s="36" t="n"/>
     </row>
     <row r="50" ht="28" customHeight="1">
       <c r="A50" s="36" t="n"/>
@@ -11484,6 +11538,7 @@
       <c r="U50" s="39" t="n"/>
       <c r="V50" s="38" t="n"/>
       <c r="W50" s="37" t="n"/>
+      <c r="X50" s="36" t="n"/>
     </row>
     <row r="51" ht="28" customHeight="1">
       <c r="A51" s="36" t="n"/>
@@ -11509,6 +11564,7 @@
       <c r="U51" s="39" t="n"/>
       <c r="V51" s="38" t="n"/>
       <c r="W51" s="37" t="n"/>
+      <c r="X51" s="36" t="n"/>
     </row>
     <row r="52" ht="28" customHeight="1">
       <c r="A52" s="36" t="n"/>
@@ -11534,6 +11590,7 @@
       <c r="U52" s="39" t="n"/>
       <c r="V52" s="38" t="n"/>
       <c r="W52" s="37" t="n"/>
+      <c r="X52" s="36" t="n"/>
     </row>
     <row r="53" ht="28" customHeight="1">
       <c r="A53" s="36" t="n"/>
@@ -11559,6 +11616,7 @@
       <c r="U53" s="39" t="n"/>
       <c r="V53" s="38" t="n"/>
       <c r="W53" s="37" t="n"/>
+      <c r="X53" s="36" t="n"/>
     </row>
     <row r="54" ht="28" customHeight="1">
       <c r="A54" s="36" t="n"/>
@@ -11584,6 +11642,7 @@
       <c r="U54" s="39" t="n"/>
       <c r="V54" s="38" t="n"/>
       <c r="W54" s="37" t="n"/>
+      <c r="X54" s="36" t="n"/>
     </row>
     <row r="55" ht="28" customHeight="1">
       <c r="A55" s="36" t="n"/>
@@ -11609,6 +11668,7 @@
       <c r="U55" s="39" t="n"/>
       <c r="V55" s="38" t="n"/>
       <c r="W55" s="37" t="n"/>
+      <c r="X55" s="36" t="n"/>
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="36" t="n"/>
@@ -11634,6 +11694,7 @@
       <c r="U56" s="39" t="n"/>
       <c r="V56" s="38" t="n"/>
       <c r="W56" s="37" t="n"/>
+      <c r="X56" s="36" t="n"/>
     </row>
     <row r="57" ht="28" customHeight="1">
       <c r="A57" s="36" t="n"/>
@@ -11659,6 +11720,7 @@
       <c r="U57" s="39" t="n"/>
       <c r="V57" s="38" t="n"/>
       <c r="W57" s="37" t="n"/>
+      <c r="X57" s="36" t="n"/>
     </row>
     <row r="58" ht="28" customHeight="1">
       <c r="A58" s="36" t="n"/>
@@ -11684,6 +11746,7 @@
       <c r="U58" s="39" t="n"/>
       <c r="V58" s="38" t="n"/>
       <c r="W58" s="37" t="n"/>
+      <c r="X58" s="36" t="n"/>
     </row>
     <row r="59" ht="28" customHeight="1">
       <c r="A59" s="36" t="n"/>
@@ -11709,6 +11772,7 @@
       <c r="U59" s="39" t="n"/>
       <c r="V59" s="38" t="n"/>
       <c r="W59" s="37" t="n"/>
+      <c r="X59" s="36" t="n"/>
     </row>
     <row r="60" ht="28" customHeight="1">
       <c r="A60" s="36" t="n"/>
@@ -11734,6 +11798,7 @@
       <c r="U60" s="39" t="n"/>
       <c r="V60" s="38" t="n"/>
       <c r="W60" s="37" t="n"/>
+      <c r="X60" s="36" t="n"/>
     </row>
     <row r="61" ht="28" customHeight="1">
       <c r="A61" s="36" t="n"/>
@@ -11759,6 +11824,7 @@
       <c r="U61" s="39" t="n"/>
       <c r="V61" s="38" t="n"/>
       <c r="W61" s="37" t="n"/>
+      <c r="X61" s="36" t="n"/>
     </row>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="36" t="n"/>
@@ -11784,6 +11850,7 @@
       <c r="U62" s="39" t="n"/>
       <c r="V62" s="38" t="n"/>
       <c r="W62" s="37" t="n"/>
+      <c r="X62" s="36" t="n"/>
     </row>
     <row r="63" ht="28" customHeight="1">
       <c r="A63" s="36" t="n"/>
@@ -11809,6 +11876,7 @@
       <c r="U63" s="39" t="n"/>
       <c r="V63" s="38" t="n"/>
       <c r="W63" s="37" t="n"/>
+      <c r="X63" s="36" t="n"/>
     </row>
     <row r="64" ht="28" customHeight="1">
       <c r="A64" s="36" t="n"/>
@@ -11834,6 +11902,7 @@
       <c r="U64" s="39" t="n"/>
       <c r="V64" s="38" t="n"/>
       <c r="W64" s="37" t="n"/>
+      <c r="X64" s="36" t="n"/>
     </row>
     <row r="65" ht="28" customHeight="1">
       <c r="A65" s="36" t="n"/>
@@ -11859,6 +11928,7 @@
       <c r="U65" s="39" t="n"/>
       <c r="V65" s="38" t="n"/>
       <c r="W65" s="37" t="n"/>
+      <c r="X65" s="36" t="n"/>
     </row>
     <row r="66" ht="28" customHeight="1">
       <c r="A66" s="36" t="n"/>
@@ -11884,6 +11954,7 @@
       <c r="U66" s="39" t="n"/>
       <c r="V66" s="38" t="n"/>
       <c r="W66" s="37" t="n"/>
+      <c r="X66" s="36" t="n"/>
     </row>
     <row r="67" ht="28" customHeight="1">
       <c r="A67" s="36" t="n"/>
@@ -11909,6 +11980,7 @@
       <c r="U67" s="39" t="n"/>
       <c r="V67" s="38" t="n"/>
       <c r="W67" s="37" t="n"/>
+      <c r="X67" s="36" t="n"/>
     </row>
     <row r="68" ht="28" customHeight="1">
       <c r="A68" s="36" t="n"/>
@@ -11934,6 +12006,7 @@
       <c r="U68" s="39" t="n"/>
       <c r="V68" s="38" t="n"/>
       <c r="W68" s="37" t="n"/>
+      <c r="X68" s="36" t="n"/>
     </row>
     <row r="69" ht="28" customHeight="1">
       <c r="A69" s="36" t="n"/>
@@ -11959,6 +12032,7 @@
       <c r="U69" s="39" t="n"/>
       <c r="V69" s="38" t="n"/>
       <c r="W69" s="37" t="n"/>
+      <c r="X69" s="36" t="n"/>
     </row>
     <row r="70" ht="28" customHeight="1">
       <c r="A70" s="36" t="n"/>
@@ -11984,6 +12058,7 @@
       <c r="U70" s="39" t="n"/>
       <c r="V70" s="38" t="n"/>
       <c r="W70" s="37" t="n"/>
+      <c r="X70" s="36" t="n"/>
     </row>
     <row r="71" ht="28" customHeight="1">
       <c r="A71" s="36" t="n"/>
@@ -12009,6 +12084,7 @@
       <c r="U71" s="39" t="n"/>
       <c r="V71" s="38" t="n"/>
       <c r="W71" s="37" t="n"/>
+      <c r="X71" s="36" t="n"/>
     </row>
     <row r="72" ht="28" customHeight="1">
       <c r="A72" s="36" t="n"/>
@@ -12034,6 +12110,7 @@
       <c r="U72" s="39" t="n"/>
       <c r="V72" s="38" t="n"/>
       <c r="W72" s="37" t="n"/>
+      <c r="X72" s="36" t="n"/>
     </row>
     <row r="73" ht="28" customHeight="1">
       <c r="A73" s="36" t="n"/>
@@ -12059,6 +12136,7 @@
       <c r="U73" s="39" t="n"/>
       <c r="V73" s="38" t="n"/>
       <c r="W73" s="37" t="n"/>
+      <c r="X73" s="36" t="n"/>
     </row>
     <row r="74" ht="28" customHeight="1">
       <c r="A74" s="36" t="n"/>
@@ -12084,6 +12162,7 @@
       <c r="U74" s="39" t="n"/>
       <c r="V74" s="38" t="n"/>
       <c r="W74" s="37" t="n"/>
+      <c r="X74" s="36" t="n"/>
     </row>
     <row r="75" ht="28" customHeight="1">
       <c r="A75" s="36" t="n"/>
@@ -12109,6 +12188,7 @@
       <c r="U75" s="39" t="n"/>
       <c r="V75" s="38" t="n"/>
       <c r="W75" s="37" t="n"/>
+      <c r="X75" s="36" t="n"/>
     </row>
     <row r="76" ht="28" customHeight="1">
       <c r="A76" s="36" t="n"/>
@@ -12134,6 +12214,7 @@
       <c r="U76" s="39" t="n"/>
       <c r="V76" s="38" t="n"/>
       <c r="W76" s="37" t="n"/>
+      <c r="X76" s="36" t="n"/>
     </row>
     <row r="77" ht="28" customHeight="1">
       <c r="A77" s="36" t="n"/>
@@ -12159,6 +12240,7 @@
       <c r="U77" s="39" t="n"/>
       <c r="V77" s="38" t="n"/>
       <c r="W77" s="37" t="n"/>
+      <c r="X77" s="36" t="n"/>
     </row>
     <row r="78" ht="28" customHeight="1">
       <c r="A78" s="36" t="n"/>
@@ -12184,6 +12266,7 @@
       <c r="U78" s="39" t="n"/>
       <c r="V78" s="38" t="n"/>
       <c r="W78" s="37" t="n"/>
+      <c r="X78" s="36" t="n"/>
     </row>
     <row r="79" ht="28" customHeight="1">
       <c r="A79" s="36" t="n"/>
@@ -12209,6 +12292,7 @@
       <c r="U79" s="39" t="n"/>
       <c r="V79" s="38" t="n"/>
       <c r="W79" s="37" t="n"/>
+      <c r="X79" s="36" t="n"/>
     </row>
     <row r="80" ht="28" customHeight="1">
       <c r="A80" s="36" t="n"/>
@@ -12234,6 +12318,7 @@
       <c r="U80" s="39" t="n"/>
       <c r="V80" s="38" t="n"/>
       <c r="W80" s="37" t="n"/>
+      <c r="X80" s="36" t="n"/>
     </row>
     <row r="81" ht="28" customHeight="1">
       <c r="A81" s="36" t="n"/>
@@ -12259,6 +12344,7 @@
       <c r="U81" s="39" t="n"/>
       <c r="V81" s="38" t="n"/>
       <c r="W81" s="37" t="n"/>
+      <c r="X81" s="36" t="n"/>
     </row>
     <row r="82" ht="28" customHeight="1">
       <c r="A82" s="36" t="n"/>
@@ -12284,6 +12370,7 @@
       <c r="U82" s="39" t="n"/>
       <c r="V82" s="38" t="n"/>
       <c r="W82" s="37" t="n"/>
+      <c r="X82" s="36" t="n"/>
     </row>
     <row r="83" ht="28" customHeight="1">
       <c r="A83" s="36" t="n"/>
@@ -12309,6 +12396,7 @@
       <c r="U83" s="39" t="n"/>
       <c r="V83" s="38" t="n"/>
       <c r="W83" s="37" t="n"/>
+      <c r="X83" s="36" t="n"/>
     </row>
     <row r="84" ht="28" customHeight="1">
       <c r="A84" s="36" t="n"/>
@@ -12334,6 +12422,7 @@
       <c r="U84" s="39" t="n"/>
       <c r="V84" s="38" t="n"/>
       <c r="W84" s="37" t="n"/>
+      <c r="X84" s="36" t="n"/>
     </row>
     <row r="85" ht="28" customHeight="1">
       <c r="A85" s="36" t="n"/>
@@ -12359,6 +12448,7 @@
       <c r="U85" s="39" t="n"/>
       <c r="V85" s="38" t="n"/>
       <c r="W85" s="37" t="n"/>
+      <c r="X85" s="36" t="n"/>
     </row>
     <row r="86" ht="28" customHeight="1">
       <c r="A86" s="36" t="n"/>
@@ -12384,6 +12474,7 @@
       <c r="U86" s="39" t="n"/>
       <c r="V86" s="38" t="n"/>
       <c r="W86" s="37" t="n"/>
+      <c r="X86" s="36" t="n"/>
     </row>
     <row r="87" ht="28" customHeight="1">
       <c r="A87" s="36" t="n"/>
@@ -12409,6 +12500,7 @@
       <c r="U87" s="39" t="n"/>
       <c r="V87" s="38" t="n"/>
       <c r="W87" s="37" t="n"/>
+      <c r="X87" s="36" t="n"/>
     </row>
     <row r="88" ht="28" customHeight="1">
       <c r="A88" s="36" t="n"/>
@@ -12434,6 +12526,7 @@
       <c r="U88" s="39" t="n"/>
       <c r="V88" s="38" t="n"/>
       <c r="W88" s="37" t="n"/>
+      <c r="X88" s="36" t="n"/>
     </row>
     <row r="89" ht="28" customHeight="1">
       <c r="A89" s="36" t="n"/>
@@ -12459,6 +12552,7 @@
       <c r="U89" s="39" t="n"/>
       <c r="V89" s="38" t="n"/>
       <c r="W89" s="37" t="n"/>
+      <c r="X89" s="36" t="n"/>
     </row>
     <row r="90" ht="28" customHeight="1">
       <c r="A90" s="36" t="n"/>
@@ -12484,6 +12578,7 @@
       <c r="U90" s="39" t="n"/>
       <c r="V90" s="38" t="n"/>
       <c r="W90" s="37" t="n"/>
+      <c r="X90" s="36" t="n"/>
     </row>
     <row r="91" ht="28" customHeight="1">
       <c r="A91" s="36" t="n"/>
@@ -12509,6 +12604,7 @@
       <c r="U91" s="39" t="n"/>
       <c r="V91" s="38" t="n"/>
       <c r="W91" s="37" t="n"/>
+      <c r="X91" s="36" t="n"/>
     </row>
     <row r="92" ht="28" customHeight="1">
       <c r="A92" s="36" t="n"/>
@@ -12534,6 +12630,7 @@
       <c r="U92" s="39" t="n"/>
       <c r="V92" s="38" t="n"/>
       <c r="W92" s="37" t="n"/>
+      <c r="X92" s="36" t="n"/>
     </row>
     <row r="93" ht="28" customHeight="1">
       <c r="A93" s="36" t="n"/>
@@ -12559,6 +12656,7 @@
       <c r="U93" s="39" t="n"/>
       <c r="V93" s="38" t="n"/>
       <c r="W93" s="37" t="n"/>
+      <c r="X93" s="36" t="n"/>
     </row>
     <row r="94" ht="28" customHeight="1">
       <c r="A94" s="36" t="n"/>
@@ -12584,6 +12682,7 @@
       <c r="U94" s="39" t="n"/>
       <c r="V94" s="38" t="n"/>
       <c r="W94" s="37" t="n"/>
+      <c r="X94" s="36" t="n"/>
     </row>
     <row r="95" ht="28" customHeight="1">
       <c r="A95" s="36" t="n"/>
@@ -12609,6 +12708,7 @@
       <c r="U95" s="39" t="n"/>
       <c r="V95" s="38" t="n"/>
       <c r="W95" s="37" t="n"/>
+      <c r="X95" s="36" t="n"/>
     </row>
     <row r="96" ht="28" customHeight="1">
       <c r="A96" s="36" t="n"/>
@@ -12634,6 +12734,7 @@
       <c r="U96" s="39" t="n"/>
       <c r="V96" s="38" t="n"/>
       <c r="W96" s="37" t="n"/>
+      <c r="X96" s="36" t="n"/>
     </row>
     <row r="97" ht="28" customHeight="1">
       <c r="A97" s="36" t="n"/>
@@ -12659,6 +12760,7 @@
       <c r="U97" s="39" t="n"/>
       <c r="V97" s="38" t="n"/>
       <c r="W97" s="37" t="n"/>
+      <c r="X97" s="36" t="n"/>
     </row>
     <row r="98" ht="28" customHeight="1">
       <c r="A98" s="36" t="n"/>
@@ -12684,6 +12786,7 @@
       <c r="U98" s="39" t="n"/>
       <c r="V98" s="38" t="n"/>
       <c r="W98" s="37" t="n"/>
+      <c r="X98" s="36" t="n"/>
     </row>
     <row r="99" ht="28" customHeight="1">
       <c r="A99" s="36" t="n"/>
@@ -12709,6 +12812,7 @@
       <c r="U99" s="39" t="n"/>
       <c r="V99" s="38" t="n"/>
       <c r="W99" s="37" t="n"/>
+      <c r="X99" s="36" t="n"/>
     </row>
     <row r="100" ht="28" customHeight="1">
       <c r="A100" s="36" t="n"/>
@@ -12734,6 +12838,7 @@
       <c r="U100" s="39" t="n"/>
       <c r="V100" s="38" t="n"/>
       <c r="W100" s="37" t="n"/>
+      <c r="X100" s="36" t="n"/>
     </row>
     <row r="101" ht="28" customHeight="1">
       <c r="A101" s="36" t="n"/>
@@ -12759,6 +12864,7 @@
       <c r="U101" s="39" t="n"/>
       <c r="V101" s="38" t="n"/>
       <c r="W101" s="37" t="n"/>
+      <c r="X101" s="36" t="n"/>
     </row>
     <row r="102" ht="28" customHeight="1">
       <c r="A102" s="36" t="n"/>
@@ -12784,6 +12890,7 @@
       <c r="U102" s="39" t="n"/>
       <c r="V102" s="38" t="n"/>
       <c r="W102" s="37" t="n"/>
+      <c r="X102" s="36" t="n"/>
     </row>
     <row r="103" ht="28" customHeight="1">
       <c r="A103" s="36" t="n"/>
@@ -12809,6 +12916,7 @@
       <c r="U103" s="39" t="n"/>
       <c r="V103" s="38" t="n"/>
       <c r="W103" s="37" t="n"/>
+      <c r="X103" s="36" t="n"/>
     </row>
     <row r="104" ht="28" customHeight="1">
       <c r="A104" s="36" t="n"/>
@@ -12834,6 +12942,7 @@
       <c r="U104" s="39" t="n"/>
       <c r="V104" s="38" t="n"/>
       <c r="W104" s="37" t="n"/>
+      <c r="X104" s="36" t="n"/>
     </row>
     <row r="105" ht="28" customHeight="1">
       <c r="A105" s="36" t="n"/>
@@ -12859,6 +12968,7 @@
       <c r="U105" s="39" t="n"/>
       <c r="V105" s="38" t="n"/>
       <c r="W105" s="37" t="n"/>
+      <c r="X105" s="36" t="n"/>
     </row>
     <row r="106" ht="28" customHeight="1">
       <c r="A106" s="36" t="n"/>
@@ -12884,6 +12994,7 @@
       <c r="U106" s="39" t="n"/>
       <c r="V106" s="38" t="n"/>
       <c r="W106" s="37" t="n"/>
+      <c r="X106" s="36" t="n"/>
     </row>
     <row r="107" ht="28" customHeight="1">
       <c r="A107" s="36" t="n"/>
@@ -12909,6 +13020,7 @@
       <c r="U107" s="39" t="n"/>
       <c r="V107" s="38" t="n"/>
       <c r="W107" s="37" t="n"/>
+      <c r="X107" s="36" t="n"/>
     </row>
     <row r="108" ht="28" customHeight="1">
       <c r="A108" s="36" t="n"/>
@@ -12934,6 +13046,7 @@
       <c r="U108" s="39" t="n"/>
       <c r="V108" s="38" t="n"/>
       <c r="W108" s="37" t="n"/>
+      <c r="X108" s="36" t="n"/>
     </row>
     <row r="109" ht="28" customHeight="1">
       <c r="A109" s="36" t="n"/>
@@ -12959,6 +13072,7 @@
       <c r="U109" s="39" t="n"/>
       <c r="V109" s="38" t="n"/>
       <c r="W109" s="37" t="n"/>
+      <c r="X109" s="36" t="n"/>
     </row>
     <row r="110" ht="28" customHeight="1">
       <c r="A110" s="36" t="n"/>
@@ -12984,6 +13098,7 @@
       <c r="U110" s="39" t="n"/>
       <c r="V110" s="38" t="n"/>
       <c r="W110" s="37" t="n"/>
+      <c r="X110" s="36" t="n"/>
     </row>
     <row r="111" ht="28" customHeight="1">
       <c r="A111" s="36" t="n"/>
@@ -13009,6 +13124,7 @@
       <c r="U111" s="39" t="n"/>
       <c r="V111" s="38" t="n"/>
       <c r="W111" s="37" t="n"/>
+      <c r="X111" s="36" t="n"/>
     </row>
     <row r="112" ht="28" customHeight="1">
       <c r="A112" s="36" t="n"/>
@@ -13034,6 +13150,7 @@
       <c r="U112" s="39" t="n"/>
       <c r="V112" s="38" t="n"/>
       <c r="W112" s="37" t="n"/>
+      <c r="X112" s="36" t="n"/>
     </row>
     <row r="113" ht="28" customHeight="1">
       <c r="A113" s="36" t="n"/>
@@ -13059,6 +13176,7 @@
       <c r="U113" s="39" t="n"/>
       <c r="V113" s="38" t="n"/>
       <c r="W113" s="37" t="n"/>
+      <c r="X113" s="36" t="n"/>
     </row>
     <row r="114" ht="28" customHeight="1">
       <c r="A114" s="36" t="n"/>
@@ -13084,6 +13202,7 @@
       <c r="U114" s="39" t="n"/>
       <c r="V114" s="38" t="n"/>
       <c r="W114" s="37" t="n"/>
+      <c r="X114" s="36" t="n"/>
     </row>
     <row r="115" ht="28" customHeight="1">
       <c r="A115" s="36" t="n"/>
@@ -13109,6 +13228,7 @@
       <c r="U115" s="39" t="n"/>
       <c r="V115" s="38" t="n"/>
       <c r="W115" s="37" t="n"/>
+      <c r="X115" s="36" t="n"/>
     </row>
     <row r="116" ht="28" customHeight="1">
       <c r="A116" s="36" t="n"/>
@@ -13134,6 +13254,7 @@
       <c r="U116" s="39" t="n"/>
       <c r="V116" s="38" t="n"/>
       <c r="W116" s="37" t="n"/>
+      <c r="X116" s="36" t="n"/>
     </row>
     <row r="117" ht="28" customHeight="1">
       <c r="A117" s="36" t="n"/>
@@ -13159,6 +13280,7 @@
       <c r="U117" s="39" t="n"/>
       <c r="V117" s="38" t="n"/>
       <c r="W117" s="37" t="n"/>
+      <c r="X117" s="36" t="n"/>
     </row>
     <row r="118" ht="28" customHeight="1">
       <c r="A118" s="36" t="n"/>
@@ -13184,6 +13306,7 @@
       <c r="U118" s="39" t="n"/>
       <c r="V118" s="38" t="n"/>
       <c r="W118" s="37" t="n"/>
+      <c r="X118" s="36" t="n"/>
     </row>
     <row r="119" ht="28" customHeight="1">
       <c r="A119" s="36" t="n"/>
@@ -13209,6 +13332,7 @@
       <c r="U119" s="39" t="n"/>
       <c r="V119" s="38" t="n"/>
       <c r="W119" s="37" t="n"/>
+      <c r="X119" s="36" t="n"/>
     </row>
     <row r="120" ht="28" customHeight="1">
       <c r="A120" s="36" t="n"/>
@@ -13234,6 +13358,7 @@
       <c r="U120" s="39" t="n"/>
       <c r="V120" s="38" t="n"/>
       <c r="W120" s="37" t="n"/>
+      <c r="X120" s="36" t="n"/>
     </row>
     <row r="121" ht="28" customHeight="1">
       <c r="A121" s="36" t="n"/>
@@ -13259,6 +13384,7 @@
       <c r="U121" s="39" t="n"/>
       <c r="V121" s="38" t="n"/>
       <c r="W121" s="37" t="n"/>
+      <c r="X121" s="36" t="n"/>
     </row>
     <row r="122" ht="28" customHeight="1">
       <c r="A122" s="36" t="n"/>
@@ -13284,6 +13410,7 @@
       <c r="U122" s="39" t="n"/>
       <c r="V122" s="38" t="n"/>
       <c r="W122" s="37" t="n"/>
+      <c r="X122" s="36" t="n"/>
     </row>
     <row r="123" ht="28" customHeight="1">
       <c r="A123" s="36" t="n"/>
@@ -13309,6 +13436,7 @@
       <c r="U123" s="39" t="n"/>
       <c r="V123" s="38" t="n"/>
       <c r="W123" s="37" t="n"/>
+      <c r="X123" s="36" t="n"/>
     </row>
     <row r="124" ht="28" customHeight="1">
       <c r="A124" s="36" t="n"/>
@@ -13334,6 +13462,7 @@
       <c r="U124" s="39" t="n"/>
       <c r="V124" s="38" t="n"/>
       <c r="W124" s="37" t="n"/>
+      <c r="X124" s="36" t="n"/>
     </row>
     <row r="125" ht="28" customHeight="1">
       <c r="A125" s="36" t="n"/>
@@ -13359,6 +13488,7 @@
       <c r="U125" s="39" t="n"/>
       <c r="V125" s="38" t="n"/>
       <c r="W125" s="37" t="n"/>
+      <c r="X125" s="36" t="n"/>
     </row>
     <row r="126" ht="28" customHeight="1">
       <c r="A126" s="36" t="n"/>
@@ -13384,6 +13514,7 @@
       <c r="U126" s="39" t="n"/>
       <c r="V126" s="38" t="n"/>
       <c r="W126" s="37" t="n"/>
+      <c r="X126" s="36" t="n"/>
     </row>
     <row r="127" ht="28" customHeight="1">
       <c r="A127" s="36" t="n"/>
@@ -13409,6 +13540,7 @@
       <c r="U127" s="39" t="n"/>
       <c r="V127" s="38" t="n"/>
       <c r="W127" s="37" t="n"/>
+      <c r="X127" s="36" t="n"/>
     </row>
     <row r="128" ht="28" customHeight="1">
       <c r="A128" s="36" t="n"/>
@@ -13434,6 +13566,7 @@
       <c r="U128" s="39" t="n"/>
       <c r="V128" s="38" t="n"/>
       <c r="W128" s="37" t="n"/>
+      <c r="X128" s="36" t="n"/>
     </row>
     <row r="129" ht="28" customHeight="1">
       <c r="A129" s="36" t="n"/>
@@ -13459,6 +13592,7 @@
       <c r="U129" s="39" t="n"/>
       <c r="V129" s="38" t="n"/>
       <c r="W129" s="37" t="n"/>
+      <c r="X129" s="36" t="n"/>
     </row>
     <row r="130" ht="28" customHeight="1">
       <c r="A130" s="36" t="n"/>
@@ -13484,6 +13618,7 @@
       <c r="U130" s="39" t="n"/>
       <c r="V130" s="38" t="n"/>
       <c r="W130" s="37" t="n"/>
+      <c r="X130" s="36" t="n"/>
     </row>
     <row r="131" ht="28" customHeight="1">
       <c r="A131" s="36" t="n"/>
@@ -13509,6 +13644,7 @@
       <c r="U131" s="39" t="n"/>
       <c r="V131" s="38" t="n"/>
       <c r="W131" s="37" t="n"/>
+      <c r="X131" s="36" t="n"/>
     </row>
     <row r="132" ht="28" customHeight="1">
       <c r="A132" s="36" t="n"/>
@@ -13534,6 +13670,7 @@
       <c r="U132" s="39" t="n"/>
       <c r="V132" s="38" t="n"/>
       <c r="W132" s="37" t="n"/>
+      <c r="X132" s="36" t="n"/>
     </row>
     <row r="133" ht="28" customHeight="1">
       <c r="A133" s="36" t="n"/>
@@ -13559,6 +13696,7 @@
       <c r="U133" s="39" t="n"/>
       <c r="V133" s="38" t="n"/>
       <c r="W133" s="37" t="n"/>
+      <c r="X133" s="36" t="n"/>
     </row>
     <row r="134" ht="28" customHeight="1">
       <c r="A134" s="36" t="n"/>
@@ -13584,6 +13722,7 @@
       <c r="U134" s="39" t="n"/>
       <c r="V134" s="38" t="n"/>
       <c r="W134" s="37" t="n"/>
+      <c r="X134" s="36" t="n"/>
     </row>
     <row r="135" ht="28" customHeight="1">
       <c r="A135" s="36" t="n"/>
@@ -13609,6 +13748,7 @@
       <c r="U135" s="39" t="n"/>
       <c r="V135" s="38" t="n"/>
       <c r="W135" s="37" t="n"/>
+      <c r="X135" s="36" t="n"/>
     </row>
     <row r="136" ht="28" customHeight="1">
       <c r="A136" s="36" t="n"/>
@@ -13634,6 +13774,7 @@
       <c r="U136" s="39" t="n"/>
       <c r="V136" s="38" t="n"/>
       <c r="W136" s="37" t="n"/>
+      <c r="X136" s="36" t="n"/>
     </row>
     <row r="137" ht="28" customHeight="1">
       <c r="A137" s="36" t="n"/>
@@ -13659,6 +13800,7 @@
       <c r="U137" s="39" t="n"/>
       <c r="V137" s="38" t="n"/>
       <c r="W137" s="37" t="n"/>
+      <c r="X137" s="36" t="n"/>
     </row>
     <row r="138" ht="28" customHeight="1">
       <c r="A138" s="36" t="n"/>
@@ -13684,6 +13826,7 @@
       <c r="U138" s="39" t="n"/>
       <c r="V138" s="38" t="n"/>
       <c r="W138" s="37" t="n"/>
+      <c r="X138" s="36" t="n"/>
     </row>
     <row r="139" ht="28" customHeight="1">
       <c r="A139" s="36" t="n"/>
@@ -13709,6 +13852,7 @@
       <c r="U139" s="39" t="n"/>
       <c r="V139" s="38" t="n"/>
       <c r="W139" s="37" t="n"/>
+      <c r="X139" s="36" t="n"/>
     </row>
     <row r="140" ht="28" customHeight="1">
       <c r="A140" s="36" t="n"/>
@@ -13734,6 +13878,7 @@
       <c r="U140" s="39" t="n"/>
       <c r="V140" s="38" t="n"/>
       <c r="W140" s="37" t="n"/>
+      <c r="X140" s="36" t="n"/>
     </row>
     <row r="141" ht="28" customHeight="1">
       <c r="A141" s="36" t="n"/>
@@ -13759,6 +13904,7 @@
       <c r="U141" s="39" t="n"/>
       <c r="V141" s="38" t="n"/>
       <c r="W141" s="37" t="n"/>
+      <c r="X141" s="36" t="n"/>
     </row>
     <row r="142" ht="28" customHeight="1">
       <c r="A142" s="36" t="n"/>
@@ -13784,6 +13930,7 @@
       <c r="U142" s="39" t="n"/>
       <c r="V142" s="38" t="n"/>
       <c r="W142" s="37" t="n"/>
+      <c r="X142" s="36" t="n"/>
     </row>
     <row r="143" ht="28" customHeight="1">
       <c r="A143" s="36" t="n"/>
@@ -13809,6 +13956,7 @@
       <c r="U143" s="39" t="n"/>
       <c r="V143" s="38" t="n"/>
       <c r="W143" s="37" t="n"/>
+      <c r="X143" s="36" t="n"/>
     </row>
     <row r="144" ht="28" customHeight="1">
       <c r="A144" s="36" t="n"/>
@@ -13834,6 +13982,7 @@
       <c r="U144" s="39" t="n"/>
       <c r="V144" s="38" t="n"/>
       <c r="W144" s="37" t="n"/>
+      <c r="X144" s="36" t="n"/>
     </row>
     <row r="145" ht="28" customHeight="1">
       <c r="A145" s="36" t="n"/>
@@ -13859,6 +14008,7 @@
       <c r="U145" s="39" t="n"/>
       <c r="V145" s="38" t="n"/>
       <c r="W145" s="37" t="n"/>
+      <c r="X145" s="36" t="n"/>
     </row>
     <row r="146" ht="28" customHeight="1">
       <c r="A146" s="36" t="n"/>
@@ -13884,6 +14034,7 @@
       <c r="U146" s="39" t="n"/>
       <c r="V146" s="38" t="n"/>
       <c r="W146" s="37" t="n"/>
+      <c r="X146" s="36" t="n"/>
     </row>
     <row r="147" ht="28" customHeight="1">
       <c r="A147" s="36" t="n"/>
@@ -13909,6 +14060,7 @@
       <c r="U147" s="39" t="n"/>
       <c r="V147" s="38" t="n"/>
       <c r="W147" s="37" t="n"/>
+      <c r="X147" s="36" t="n"/>
     </row>
     <row r="148" ht="28" customHeight="1">
       <c r="A148" s="36" t="n"/>
@@ -13934,6 +14086,7 @@
       <c r="U148" s="39" t="n"/>
       <c r="V148" s="38" t="n"/>
       <c r="W148" s="37" t="n"/>
+      <c r="X148" s="36" t="n"/>
     </row>
     <row r="149" ht="28" customHeight="1">
       <c r="A149" s="36" t="n"/>
@@ -13959,6 +14112,7 @@
       <c r="U149" s="39" t="n"/>
       <c r="V149" s="38" t="n"/>
       <c r="W149" s="37" t="n"/>
+      <c r="X149" s="36" t="n"/>
     </row>
     <row r="150" ht="28" customHeight="1">
       <c r="A150" s="36" t="n"/>
@@ -13984,6 +14138,7 @@
       <c r="U150" s="39" t="n"/>
       <c r="V150" s="38" t="n"/>
       <c r="W150" s="37" t="n"/>
+      <c r="X150" s="36" t="n"/>
     </row>
     <row r="151" ht="28" customHeight="1">
       <c r="A151" s="36" t="n"/>
@@ -14009,6 +14164,7 @@
       <c r="U151" s="39" t="n"/>
       <c r="V151" s="38" t="n"/>
       <c r="W151" s="37" t="n"/>
+      <c r="X151" s="36" t="n"/>
     </row>
     <row r="152" ht="28" customHeight="1">
       <c r="A152" s="36" t="n"/>
@@ -14034,6 +14190,7 @@
       <c r="U152" s="39" t="n"/>
       <c r="V152" s="38" t="n"/>
       <c r="W152" s="37" t="n"/>
+      <c r="X152" s="36" t="n"/>
     </row>
     <row r="153" ht="28" customHeight="1">
       <c r="A153" s="36" t="n"/>
@@ -14059,6 +14216,7 @@
       <c r="U153" s="39" t="n"/>
       <c r="V153" s="38" t="n"/>
       <c r="W153" s="37" t="n"/>
+      <c r="X153" s="36" t="n"/>
     </row>
     <row r="154" ht="28" customHeight="1">
       <c r="A154" s="36" t="n"/>
@@ -14084,6 +14242,7 @@
       <c r="U154" s="39" t="n"/>
       <c r="V154" s="38" t="n"/>
       <c r="W154" s="37" t="n"/>
+      <c r="X154" s="36" t="n"/>
     </row>
     <row r="155" ht="28" customHeight="1">
       <c r="A155" s="36" t="n"/>
@@ -14109,6 +14268,7 @@
       <c r="U155" s="39" t="n"/>
       <c r="V155" s="38" t="n"/>
       <c r="W155" s="37" t="n"/>
+      <c r="X155" s="36" t="n"/>
     </row>
     <row r="156" ht="28" customHeight="1">
       <c r="A156" s="36" t="n"/>
@@ -14134,6 +14294,7 @@
       <c r="U156" s="39" t="n"/>
       <c r="V156" s="38" t="n"/>
       <c r="W156" s="37" t="n"/>
+      <c r="X156" s="36" t="n"/>
     </row>
     <row r="157" ht="28" customHeight="1">
       <c r="A157" s="36" t="n"/>
@@ -14159,6 +14320,7 @@
       <c r="U157" s="39" t="n"/>
       <c r="V157" s="38" t="n"/>
       <c r="W157" s="37" t="n"/>
+      <c r="X157" s="36" t="n"/>
     </row>
     <row r="158" ht="28" customHeight="1">
       <c r="A158" s="36" t="n"/>
@@ -14184,6 +14346,7 @@
       <c r="U158" s="39" t="n"/>
       <c r="V158" s="38" t="n"/>
       <c r="W158" s="37" t="n"/>
+      <c r="X158" s="36" t="n"/>
     </row>
     <row r="159" ht="28" customHeight="1">
       <c r="A159" s="36" t="n"/>
@@ -14209,6 +14372,7 @@
       <c r="U159" s="39" t="n"/>
       <c r="V159" s="38" t="n"/>
       <c r="W159" s="37" t="n"/>
+      <c r="X159" s="36" t="n"/>
     </row>
     <row r="160" ht="28" customHeight="1">
       <c r="A160" s="36" t="n"/>
@@ -14234,6 +14398,7 @@
       <c r="U160" s="39" t="n"/>
       <c r="V160" s="38" t="n"/>
       <c r="W160" s="37" t="n"/>
+      <c r="X160" s="36" t="n"/>
     </row>
     <row r="161" ht="28" customHeight="1">
       <c r="A161" s="36" t="n"/>
@@ -14259,6 +14424,7 @@
       <c r="U161" s="39" t="n"/>
       <c r="V161" s="38" t="n"/>
       <c r="W161" s="37" t="n"/>
+      <c r="X161" s="36" t="n"/>
     </row>
     <row r="162" ht="28" customHeight="1">
       <c r="A162" s="36" t="n"/>
@@ -14284,6 +14450,7 @@
       <c r="U162" s="39" t="n"/>
       <c r="V162" s="38" t="n"/>
       <c r="W162" s="37" t="n"/>
+      <c r="X162" s="36" t="n"/>
     </row>
     <row r="163" ht="28" customHeight="1">
       <c r="A163" s="36" t="n"/>
@@ -14309,6 +14476,7 @@
       <c r="U163" s="39" t="n"/>
       <c r="V163" s="38" t="n"/>
       <c r="W163" s="37" t="n"/>
+      <c r="X163" s="36" t="n"/>
     </row>
     <row r="164" ht="28" customHeight="1">
       <c r="A164" s="36" t="n"/>
@@ -14334,6 +14502,7 @@
       <c r="U164" s="39" t="n"/>
       <c r="V164" s="38" t="n"/>
       <c r="W164" s="37" t="n"/>
+      <c r="X164" s="36" t="n"/>
     </row>
     <row r="165" ht="28" customHeight="1">
       <c r="A165" s="36" t="n"/>
@@ -14359,6 +14528,7 @@
       <c r="U165" s="39" t="n"/>
       <c r="V165" s="38" t="n"/>
       <c r="W165" s="37" t="n"/>
+      <c r="X165" s="36" t="n"/>
     </row>
     <row r="166" ht="28" customHeight="1">
       <c r="A166" s="36" t="n"/>
@@ -14384,6 +14554,7 @@
       <c r="U166" s="39" t="n"/>
       <c r="V166" s="38" t="n"/>
       <c r="W166" s="37" t="n"/>
+      <c r="X166" s="36" t="n"/>
     </row>
     <row r="167" ht="28" customHeight="1">
       <c r="A167" s="36" t="n"/>
@@ -14409,6 +14580,7 @@
       <c r="U167" s="39" t="n"/>
       <c r="V167" s="38" t="n"/>
       <c r="W167" s="37" t="n"/>
+      <c r="X167" s="36" t="n"/>
     </row>
     <row r="168" ht="28" customHeight="1">
       <c r="A168" s="36" t="n"/>
@@ -14434,6 +14606,7 @@
       <c r="U168" s="39" t="n"/>
       <c r="V168" s="38" t="n"/>
       <c r="W168" s="37" t="n"/>
+      <c r="X168" s="36" t="n"/>
     </row>
     <row r="169" ht="28" customHeight="1">
       <c r="A169" s="36" t="n"/>
@@ -14459,6 +14632,7 @@
       <c r="U169" s="39" t="n"/>
       <c r="V169" s="38" t="n"/>
       <c r="W169" s="37" t="n"/>
+      <c r="X169" s="36" t="n"/>
     </row>
     <row r="170" ht="28" customHeight="1">
       <c r="A170" s="36" t="n"/>
@@ -14484,6 +14658,7 @@
       <c r="U170" s="39" t="n"/>
       <c r="V170" s="38" t="n"/>
       <c r="W170" s="37" t="n"/>
+      <c r="X170" s="36" t="n"/>
     </row>
     <row r="171" ht="28" customHeight="1">
       <c r="A171" s="36" t="n"/>
@@ -14509,6 +14684,7 @@
       <c r="U171" s="39" t="n"/>
       <c r="V171" s="38" t="n"/>
       <c r="W171" s="37" t="n"/>
+      <c r="X171" s="36" t="n"/>
     </row>
     <row r="172" ht="28" customHeight="1">
       <c r="A172" s="36" t="n"/>
@@ -14534,6 +14710,7 @@
       <c r="U172" s="39" t="n"/>
       <c r="V172" s="38" t="n"/>
       <c r="W172" s="37" t="n"/>
+      <c r="X172" s="36" t="n"/>
     </row>
     <row r="173" ht="28" customHeight="1">
       <c r="A173" s="36" t="n"/>
@@ -14559,6 +14736,7 @@
       <c r="U173" s="39" t="n"/>
       <c r="V173" s="38" t="n"/>
       <c r="W173" s="37" t="n"/>
+      <c r="X173" s="36" t="n"/>
     </row>
     <row r="174" ht="28" customHeight="1">
       <c r="A174" s="36" t="n"/>
@@ -14584,6 +14762,7 @@
       <c r="U174" s="39" t="n"/>
       <c r="V174" s="38" t="n"/>
       <c r="W174" s="37" t="n"/>
+      <c r="X174" s="36" t="n"/>
     </row>
     <row r="175" ht="28" customHeight="1">
       <c r="A175" s="36" t="n"/>
@@ -14609,6 +14788,7 @@
       <c r="U175" s="39" t="n"/>
       <c r="V175" s="38" t="n"/>
       <c r="W175" s="37" t="n"/>
+      <c r="X175" s="36" t="n"/>
     </row>
     <row r="176" ht="28" customHeight="1">
       <c r="A176" s="36" t="n"/>
@@ -14634,6 +14814,7 @@
       <c r="U176" s="39" t="n"/>
       <c r="V176" s="38" t="n"/>
       <c r="W176" s="37" t="n"/>
+      <c r="X176" s="36" t="n"/>
     </row>
     <row r="177" ht="28" customHeight="1">
       <c r="A177" s="36" t="n"/>
@@ -14659,6 +14840,7 @@
       <c r="U177" s="39" t="n"/>
       <c r="V177" s="38" t="n"/>
       <c r="W177" s="37" t="n"/>
+      <c r="X177" s="36" t="n"/>
     </row>
     <row r="178" ht="28" customHeight="1">
       <c r="A178" s="36" t="n"/>
@@ -14684,6 +14866,7 @@
       <c r="U178" s="39" t="n"/>
       <c r="V178" s="38" t="n"/>
       <c r="W178" s="37" t="n"/>
+      <c r="X178" s="36" t="n"/>
     </row>
     <row r="179" ht="28" customHeight="1">
       <c r="A179" s="36" t="n"/>
@@ -14709,6 +14892,7 @@
       <c r="U179" s="39" t="n"/>
       <c r="V179" s="38" t="n"/>
       <c r="W179" s="37" t="n"/>
+      <c r="X179" s="36" t="n"/>
     </row>
     <row r="180" ht="28" customHeight="1">
       <c r="A180" s="36" t="n"/>
@@ -14734,6 +14918,7 @@
       <c r="U180" s="39" t="n"/>
       <c r="V180" s="38" t="n"/>
       <c r="W180" s="37" t="n"/>
+      <c r="X180" s="36" t="n"/>
     </row>
     <row r="181" ht="28" customHeight="1">
       <c r="A181" s="36" t="n"/>
@@ -14759,6 +14944,7 @@
       <c r="U181" s="39" t="n"/>
       <c r="V181" s="38" t="n"/>
       <c r="W181" s="37" t="n"/>
+      <c r="X181" s="36" t="n"/>
     </row>
     <row r="182" ht="28" customHeight="1">
       <c r="A182" s="36" t="n"/>
@@ -14784,6 +14970,7 @@
       <c r="U182" s="39" t="n"/>
       <c r="V182" s="38" t="n"/>
       <c r="W182" s="37" t="n"/>
+      <c r="X182" s="36" t="n"/>
     </row>
     <row r="183" ht="28" customHeight="1">
       <c r="A183" s="36" t="n"/>
@@ -14809,6 +14996,7 @@
       <c r="U183" s="39" t="n"/>
       <c r="V183" s="38" t="n"/>
       <c r="W183" s="37" t="n"/>
+      <c r="X183" s="36" t="n"/>
     </row>
     <row r="184" ht="28" customHeight="1">
       <c r="A184" s="36" t="n"/>
@@ -14834,6 +15022,7 @@
       <c r="U184" s="39" t="n"/>
       <c r="V184" s="38" t="n"/>
       <c r="W184" s="37" t="n"/>
+      <c r="X184" s="36" t="n"/>
     </row>
     <row r="185" ht="28" customHeight="1">
       <c r="A185" s="36" t="n"/>
@@ -14859,6 +15048,7 @@
       <c r="U185" s="39" t="n"/>
       <c r="V185" s="38" t="n"/>
       <c r="W185" s="37" t="n"/>
+      <c r="X185" s="36" t="n"/>
     </row>
     <row r="186" ht="28" customHeight="1">
       <c r="A186" s="36" t="n"/>
@@ -14884,6 +15074,7 @@
       <c r="U186" s="39" t="n"/>
       <c r="V186" s="38" t="n"/>
       <c r="W186" s="37" t="n"/>
+      <c r="X186" s="36" t="n"/>
     </row>
     <row r="187" ht="28" customHeight="1">
       <c r="A187" s="36" t="n"/>
@@ -14909,6 +15100,7 @@
       <c r="U187" s="39" t="n"/>
       <c r="V187" s="38" t="n"/>
       <c r="W187" s="37" t="n"/>
+      <c r="X187" s="36" t="n"/>
     </row>
     <row r="188" ht="28" customHeight="1">
       <c r="A188" s="36" t="n"/>
@@ -14934,6 +15126,7 @@
       <c r="U188" s="39" t="n"/>
       <c r="V188" s="38" t="n"/>
       <c r="W188" s="37" t="n"/>
+      <c r="X188" s="36" t="n"/>
     </row>
     <row r="189" ht="28" customHeight="1">
       <c r="A189" s="36" t="n"/>
@@ -14959,6 +15152,7 @@
       <c r="U189" s="39" t="n"/>
       <c r="V189" s="38" t="n"/>
       <c r="W189" s="37" t="n"/>
+      <c r="X189" s="36" t="n"/>
     </row>
     <row r="190" ht="28" customHeight="1">
       <c r="A190" s="36" t="n"/>
@@ -14984,6 +15178,7 @@
       <c r="U190" s="39" t="n"/>
       <c r="V190" s="38" t="n"/>
       <c r="W190" s="37" t="n"/>
+      <c r="X190" s="36" t="n"/>
     </row>
     <row r="191" ht="28" customHeight="1">
       <c r="A191" s="36" t="n"/>
@@ -15009,6 +15204,7 @@
       <c r="U191" s="39" t="n"/>
       <c r="V191" s="38" t="n"/>
       <c r="W191" s="37" t="n"/>
+      <c r="X191" s="36" t="n"/>
     </row>
     <row r="192" ht="28" customHeight="1">
       <c r="A192" s="36" t="n"/>
@@ -15034,6 +15230,7 @@
       <c r="U192" s="39" t="n"/>
       <c r="V192" s="38" t="n"/>
       <c r="W192" s="37" t="n"/>
+      <c r="X192" s="36" t="n"/>
     </row>
     <row r="193" ht="28" customHeight="1">
       <c r="A193" s="36" t="n"/>
@@ -15059,6 +15256,7 @@
       <c r="U193" s="39" t="n"/>
       <c r="V193" s="38" t="n"/>
       <c r="W193" s="37" t="n"/>
+      <c r="X193" s="36" t="n"/>
     </row>
     <row r="194" ht="28" customHeight="1">
       <c r="A194" s="36" t="n"/>
@@ -15084,6 +15282,7 @@
       <c r="U194" s="39" t="n"/>
       <c r="V194" s="38" t="n"/>
       <c r="W194" s="37" t="n"/>
+      <c r="X194" s="36" t="n"/>
     </row>
     <row r="195" ht="28" customHeight="1">
       <c r="A195" s="36" t="n"/>
@@ -15109,6 +15308,7 @@
       <c r="U195" s="39" t="n"/>
       <c r="V195" s="38" t="n"/>
       <c r="W195" s="37" t="n"/>
+      <c r="X195" s="36" t="n"/>
     </row>
     <row r="196" ht="28" customHeight="1">
       <c r="A196" s="36" t="n"/>
@@ -15134,6 +15334,7 @@
       <c r="U196" s="39" t="n"/>
       <c r="V196" s="38" t="n"/>
       <c r="W196" s="37" t="n"/>
+      <c r="X196" s="36" t="n"/>
     </row>
     <row r="197" ht="28" customHeight="1">
       <c r="A197" s="36" t="n"/>
@@ -15159,6 +15360,7 @@
       <c r="U197" s="39" t="n"/>
       <c r="V197" s="38" t="n"/>
       <c r="W197" s="37" t="n"/>
+      <c r="X197" s="36" t="n"/>
     </row>
     <row r="198" ht="28" customHeight="1">
       <c r="A198" s="36" t="n"/>
@@ -15184,6 +15386,7 @@
       <c r="U198" s="39" t="n"/>
       <c r="V198" s="38" t="n"/>
       <c r="W198" s="37" t="n"/>
+      <c r="X198" s="36" t="n"/>
     </row>
     <row r="199" ht="28" customHeight="1">
       <c r="A199" s="36" t="n"/>
@@ -15209,6 +15412,7 @@
       <c r="U199" s="39" t="n"/>
       <c r="V199" s="38" t="n"/>
       <c r="W199" s="37" t="n"/>
+      <c r="X199" s="36" t="n"/>
     </row>
     <row r="200" ht="28" customHeight="1">
       <c r="A200" s="36" t="n"/>
@@ -15234,6 +15438,7 @@
       <c r="U200" s="39" t="n"/>
       <c r="V200" s="38" t="n"/>
       <c r="W200" s="37" t="n"/>
+      <c r="X200" s="36" t="n"/>
     </row>
     <row r="201" ht="28" customHeight="1">
       <c r="A201" s="36" t="n"/>
@@ -15259,6 +15464,7 @@
       <c r="U201" s="39" t="n"/>
       <c r="V201" s="38" t="n"/>
       <c r="W201" s="37" t="n"/>
+      <c r="X201" s="36" t="n"/>
     </row>
     <row r="202" ht="28" customHeight="1">
       <c r="A202" s="36" t="n"/>
@@ -15284,6 +15490,7 @@
       <c r="U202" s="39" t="n"/>
       <c r="V202" s="38" t="n"/>
       <c r="W202" s="37" t="n"/>
+      <c r="X202" s="36" t="n"/>
     </row>
     <row r="203" ht="28" customHeight="1">
       <c r="A203" s="36" t="n"/>
@@ -15309,6 +15516,7 @@
       <c r="U203" s="39" t="n"/>
       <c r="V203" s="38" t="n"/>
       <c r="W203" s="37" t="n"/>
+      <c r="X203" s="36" t="n"/>
     </row>
     <row r="204" ht="28" customHeight="1">
       <c r="A204" s="36" t="n"/>
@@ -15334,6 +15542,7 @@
       <c r="U204" s="39" t="n"/>
       <c r="V204" s="38" t="n"/>
       <c r="W204" s="37" t="n"/>
+      <c r="X204" s="36" t="n"/>
     </row>
     <row r="205" ht="28" customHeight="1">
       <c r="A205" s="36" t="n"/>
@@ -15359,6 +15568,7 @@
       <c r="U205" s="39" t="n"/>
       <c r="V205" s="38" t="n"/>
       <c r="W205" s="37" t="n"/>
+      <c r="X205" s="36" t="n"/>
     </row>
     <row r="206" ht="28" customHeight="1">
       <c r="A206" s="36" t="n"/>
@@ -15384,6 +15594,7 @@
       <c r="U206" s="39" t="n"/>
       <c r="V206" s="38" t="n"/>
       <c r="W206" s="37" t="n"/>
+      <c r="X206" s="36" t="n"/>
     </row>
     <row r="207" ht="28" customHeight="1">
       <c r="A207" s="36" t="n"/>
@@ -15409,6 +15620,7 @@
       <c r="U207" s="39" t="n"/>
       <c r="V207" s="38" t="n"/>
       <c r="W207" s="37" t="n"/>
+      <c r="X207" s="36" t="n"/>
     </row>
     <row r="208" ht="28" customHeight="1">
       <c r="A208" s="36" t="n"/>
@@ -15434,6 +15646,7 @@
       <c r="U208" s="39" t="n"/>
       <c r="V208" s="38" t="n"/>
       <c r="W208" s="37" t="n"/>
+      <c r="X208" s="36" t="n"/>
     </row>
     <row r="209" ht="28" customHeight="1">
       <c r="A209" s="36" t="n"/>
@@ -15459,6 +15672,7 @@
       <c r="U209" s="39" t="n"/>
       <c r="V209" s="38" t="n"/>
       <c r="W209" s="37" t="n"/>
+      <c r="X209" s="36" t="n"/>
     </row>
     <row r="210" ht="28" customHeight="1">
       <c r="A210" s="36" t="n"/>
@@ -15484,6 +15698,7 @@
       <c r="U210" s="39" t="n"/>
       <c r="V210" s="38" t="n"/>
       <c r="W210" s="37" t="n"/>
+      <c r="X210" s="36" t="n"/>
     </row>
     <row r="211" ht="28" customHeight="1">
       <c r="A211" s="36" t="n"/>
@@ -15509,6 +15724,7 @@
       <c r="U211" s="39" t="n"/>
       <c r="V211" s="38" t="n"/>
       <c r="W211" s="37" t="n"/>
+      <c r="X211" s="36" t="n"/>
     </row>
     <row r="212" ht="28" customHeight="1">
       <c r="A212" s="36" t="n"/>
@@ -15534,6 +15750,7 @@
       <c r="U212" s="39" t="n"/>
       <c r="V212" s="38" t="n"/>
       <c r="W212" s="37" t="n"/>
+      <c r="X212" s="36" t="n"/>
     </row>
     <row r="213" ht="28" customHeight="1">
       <c r="A213" s="36" t="n"/>
@@ -15559,6 +15776,7 @@
       <c r="U213" s="39" t="n"/>
       <c r="V213" s="38" t="n"/>
       <c r="W213" s="37" t="n"/>
+      <c r="X213" s="36" t="n"/>
     </row>
     <row r="214" ht="28" customHeight="1">
       <c r="A214" s="36" t="n"/>
@@ -15584,6 +15802,7 @@
       <c r="U214" s="39" t="n"/>
       <c r="V214" s="38" t="n"/>
       <c r="W214" s="37" t="n"/>
+      <c r="X214" s="36" t="n"/>
     </row>
     <row r="215" ht="28" customHeight="1">
       <c r="A215" s="36" t="n"/>
@@ -15609,6 +15828,7 @@
       <c r="U215" s="39" t="n"/>
       <c r="V215" s="38" t="n"/>
       <c r="W215" s="37" t="n"/>
+      <c r="X215" s="36" t="n"/>
     </row>
     <row r="216" ht="28" customHeight="1">
       <c r="A216" s="36" t="n"/>
@@ -15634,6 +15854,7 @@
       <c r="U216" s="39" t="n"/>
       <c r="V216" s="38" t="n"/>
       <c r="W216" s="37" t="n"/>
+      <c r="X216" s="36" t="n"/>
     </row>
     <row r="217" ht="28" customHeight="1">
       <c r="A217" s="36" t="n"/>
@@ -15659,6 +15880,7 @@
       <c r="U217" s="39" t="n"/>
       <c r="V217" s="38" t="n"/>
       <c r="W217" s="37" t="n"/>
+      <c r="X217" s="36" t="n"/>
     </row>
     <row r="218" ht="28" customHeight="1">
       <c r="A218" s="36" t="n"/>
@@ -15684,6 +15906,7 @@
       <c r="U218" s="39" t="n"/>
       <c r="V218" s="38" t="n"/>
       <c r="W218" s="37" t="n"/>
+      <c r="X218" s="36" t="n"/>
     </row>
     <row r="219" ht="28" customHeight="1">
       <c r="A219" s="36" t="n"/>
@@ -15709,6 +15932,7 @@
       <c r="U219" s="39" t="n"/>
       <c r="V219" s="38" t="n"/>
       <c r="W219" s="37" t="n"/>
+      <c r="X219" s="36" t="n"/>
     </row>
     <row r="220" ht="28" customHeight="1">
       <c r="A220" s="36" t="n"/>
@@ -15734,6 +15958,7 @@
       <c r="U220" s="39" t="n"/>
       <c r="V220" s="38" t="n"/>
       <c r="W220" s="37" t="n"/>
+      <c r="X220" s="36" t="n"/>
     </row>
     <row r="221" ht="28" customHeight="1">
       <c r="A221" s="36" t="n"/>
@@ -15759,6 +15984,7 @@
       <c r="U221" s="39" t="n"/>
       <c r="V221" s="38" t="n"/>
       <c r="W221" s="37" t="n"/>
+      <c r="X221" s="36" t="n"/>
     </row>
     <row r="222" ht="28" customHeight="1">
       <c r="A222" s="36" t="n"/>
@@ -15784,6 +16010,7 @@
       <c r="U222" s="39" t="n"/>
       <c r="V222" s="38" t="n"/>
       <c r="W222" s="37" t="n"/>
+      <c r="X222" s="36" t="n"/>
     </row>
     <row r="223" ht="28" customHeight="1">
       <c r="A223" s="36" t="n"/>
@@ -15809,6 +16036,7 @@
       <c r="U223" s="39" t="n"/>
       <c r="V223" s="38" t="n"/>
       <c r="W223" s="37" t="n"/>
+      <c r="X223" s="36" t="n"/>
     </row>
     <row r="224" ht="28" customHeight="1">
       <c r="A224" s="36" t="n"/>
@@ -15834,6 +16062,7 @@
       <c r="U224" s="39" t="n"/>
       <c r="V224" s="38" t="n"/>
       <c r="W224" s="37" t="n"/>
+      <c r="X224" s="36" t="n"/>
     </row>
     <row r="225" ht="28" customHeight="1">
       <c r="A225" s="36" t="n"/>
@@ -15859,6 +16088,7 @@
       <c r="U225" s="39" t="n"/>
       <c r="V225" s="38" t="n"/>
       <c r="W225" s="37" t="n"/>
+      <c r="X225" s="36" t="n"/>
     </row>
     <row r="226" ht="28" customHeight="1">
       <c r="A226" s="36" t="n"/>
@@ -15884,6 +16114,7 @@
       <c r="U226" s="39" t="n"/>
       <c r="V226" s="38" t="n"/>
       <c r="W226" s="37" t="n"/>
+      <c r="X226" s="36" t="n"/>
     </row>
     <row r="227" ht="28" customHeight="1">
       <c r="A227" s="36" t="n"/>
@@ -15909,6 +16140,7 @@
       <c r="U227" s="39" t="n"/>
       <c r="V227" s="38" t="n"/>
       <c r="W227" s="37" t="n"/>
+      <c r="X227" s="36" t="n"/>
     </row>
     <row r="228" ht="28" customHeight="1">
       <c r="A228" s="36" t="n"/>
@@ -15934,6 +16166,7 @@
       <c r="U228" s="39" t="n"/>
       <c r="V228" s="38" t="n"/>
       <c r="W228" s="37" t="n"/>
+      <c r="X228" s="36" t="n"/>
     </row>
     <row r="229" ht="28" customHeight="1">
       <c r="A229" s="36" t="n"/>
@@ -15959,6 +16192,7 @@
       <c r="U229" s="39" t="n"/>
       <c r="V229" s="38" t="n"/>
       <c r="W229" s="37" t="n"/>
+      <c r="X229" s="36" t="n"/>
     </row>
     <row r="230" ht="28" customHeight="1">
       <c r="A230" s="36" t="n"/>
@@ -15984,6 +16218,7 @@
       <c r="U230" s="39" t="n"/>
       <c r="V230" s="38" t="n"/>
       <c r="W230" s="37" t="n"/>
+      <c r="X230" s="36" t="n"/>
     </row>
     <row r="231" ht="28" customHeight="1">
       <c r="A231" s="36" t="n"/>
@@ -16009,6 +16244,7 @@
       <c r="U231" s="39" t="n"/>
       <c r="V231" s="38" t="n"/>
       <c r="W231" s="37" t="n"/>
+      <c r="X231" s="36" t="n"/>
     </row>
     <row r="232" ht="28" customHeight="1">
       <c r="A232" s="36" t="n"/>
@@ -16034,6 +16270,7 @@
       <c r="U232" s="39" t="n"/>
       <c r="V232" s="38" t="n"/>
       <c r="W232" s="37" t="n"/>
+      <c r="X232" s="36" t="n"/>
     </row>
     <row r="233" ht="28" customHeight="1">
       <c r="A233" s="36" t="n"/>
@@ -16059,6 +16296,7 @@
       <c r="U233" s="39" t="n"/>
       <c r="V233" s="38" t="n"/>
       <c r="W233" s="37" t="n"/>
+      <c r="X233" s="36" t="n"/>
     </row>
     <row r="234" ht="28" customHeight="1">
       <c r="A234" s="36" t="n"/>
@@ -16084,6 +16322,7 @@
       <c r="U234" s="39" t="n"/>
       <c r="V234" s="38" t="n"/>
       <c r="W234" s="37" t="n"/>
+      <c r="X234" s="36" t="n"/>
     </row>
     <row r="235" ht="28" customHeight="1">
       <c r="A235" s="36" t="n"/>
@@ -16109,6 +16348,7 @@
       <c r="U235" s="39" t="n"/>
       <c r="V235" s="38" t="n"/>
       <c r="W235" s="37" t="n"/>
+      <c r="X235" s="36" t="n"/>
     </row>
     <row r="236" ht="28" customHeight="1">
       <c r="A236" s="36" t="n"/>
@@ -16134,6 +16374,7 @@
       <c r="U236" s="39" t="n"/>
       <c r="V236" s="38" t="n"/>
       <c r="W236" s="37" t="n"/>
+      <c r="X236" s="36" t="n"/>
     </row>
     <row r="237" ht="28" customHeight="1">
       <c r="A237" s="36" t="n"/>
@@ -16159,6 +16400,7 @@
       <c r="U237" s="39" t="n"/>
       <c r="V237" s="38" t="n"/>
       <c r="W237" s="37" t="n"/>
+      <c r="X237" s="36" t="n"/>
     </row>
     <row r="238" ht="28" customHeight="1">
       <c r="A238" s="36" t="n"/>
@@ -16184,6 +16426,7 @@
       <c r="U238" s="39" t="n"/>
       <c r="V238" s="38" t="n"/>
       <c r="W238" s="37" t="n"/>
+      <c r="X238" s="36" t="n"/>
     </row>
     <row r="239" ht="28" customHeight="1">
       <c r="A239" s="36" t="n"/>
@@ -16209,6 +16452,7 @@
       <c r="U239" s="39" t="n"/>
       <c r="V239" s="38" t="n"/>
       <c r="W239" s="37" t="n"/>
+      <c r="X239" s="36" t="n"/>
     </row>
     <row r="240" ht="28" customHeight="1">
       <c r="A240" s="36" t="n"/>
@@ -16234,6 +16478,7 @@
       <c r="U240" s="39" t="n"/>
       <c r="V240" s="38" t="n"/>
       <c r="W240" s="37" t="n"/>
+      <c r="X240" s="36" t="n"/>
     </row>
     <row r="241" ht="28" customHeight="1">
       <c r="A241" s="36" t="n"/>
@@ -16259,6 +16504,7 @@
       <c r="U241" s="39" t="n"/>
       <c r="V241" s="38" t="n"/>
       <c r="W241" s="37" t="n"/>
+      <c r="X241" s="36" t="n"/>
     </row>
     <row r="242" ht="28" customHeight="1">
       <c r="A242" s="36" t="n"/>
@@ -16284,6 +16530,7 @@
       <c r="U242" s="39" t="n"/>
       <c r="V242" s="38" t="n"/>
       <c r="W242" s="37" t="n"/>
+      <c r="X242" s="36" t="n"/>
     </row>
     <row r="243" ht="28" customHeight="1">
       <c r="A243" s="36" t="n"/>
@@ -16309,6 +16556,7 @@
       <c r="U243" s="39" t="n"/>
       <c r="V243" s="38" t="n"/>
       <c r="W243" s="37" t="n"/>
+      <c r="X243" s="36" t="n"/>
     </row>
     <row r="244" ht="28" customHeight="1">
       <c r="A244" s="36" t="n"/>
@@ -16334,6 +16582,7 @@
       <c r="U244" s="39" t="n"/>
       <c r="V244" s="38" t="n"/>
       <c r="W244" s="37" t="n"/>
+      <c r="X244" s="36" t="n"/>
     </row>
     <row r="245" ht="28" customHeight="1">
       <c r="A245" s="36" t="n"/>
@@ -16359,6 +16608,7 @@
       <c r="U245" s="39" t="n"/>
       <c r="V245" s="38" t="n"/>
       <c r="W245" s="37" t="n"/>
+      <c r="X245" s="36" t="n"/>
     </row>
     <row r="246" ht="28" customHeight="1">
       <c r="A246" s="36" t="n"/>
@@ -16384,6 +16634,7 @@
       <c r="U246" s="39" t="n"/>
       <c r="V246" s="38" t="n"/>
       <c r="W246" s="37" t="n"/>
+      <c r="X246" s="36" t="n"/>
     </row>
     <row r="247" ht="28" customHeight="1">
       <c r="A247" s="36" t="n"/>
@@ -16409,6 +16660,7 @@
       <c r="U247" s="39" t="n"/>
       <c r="V247" s="38" t="n"/>
       <c r="W247" s="37" t="n"/>
+      <c r="X247" s="36" t="n"/>
     </row>
     <row r="248" ht="28" customHeight="1">
       <c r="A248" s="36" t="n"/>
@@ -16434,6 +16686,7 @@
       <c r="U248" s="39" t="n"/>
       <c r="V248" s="38" t="n"/>
       <c r="W248" s="37" t="n"/>
+      <c r="X248" s="36" t="n"/>
     </row>
     <row r="249" ht="28" customHeight="1">
       <c r="A249" s="36" t="n"/>
@@ -16459,6 +16712,7 @@
       <c r="U249" s="39" t="n"/>
       <c r="V249" s="38" t="n"/>
       <c r="W249" s="37" t="n"/>
+      <c r="X249" s="36" t="n"/>
     </row>
     <row r="250" ht="28" customHeight="1">
       <c r="A250" s="36" t="n"/>
@@ -16484,6 +16738,7 @@
       <c r="U250" s="39" t="n"/>
       <c r="V250" s="38" t="n"/>
       <c r="W250" s="37" t="n"/>
+      <c r="X250" s="36" t="n"/>
     </row>
     <row r="251" ht="28" customHeight="1">
       <c r="A251" s="36" t="n"/>
@@ -16509,6 +16764,7 @@
       <c r="U251" s="39" t="n"/>
       <c r="V251" s="38" t="n"/>
       <c r="W251" s="37" t="n"/>
+      <c r="X251" s="36" t="n"/>
     </row>
     <row r="252" ht="28" customHeight="1">
       <c r="A252" s="36" t="n"/>
@@ -16534,6 +16790,7 @@
       <c r="U252" s="39" t="n"/>
       <c r="V252" s="38" t="n"/>
       <c r="W252" s="37" t="n"/>
+      <c r="X252" s="36" t="n"/>
     </row>
     <row r="253" ht="28" customHeight="1">
       <c r="A253" s="36" t="n"/>
@@ -16559,6 +16816,7 @@
       <c r="U253" s="39" t="n"/>
       <c r="V253" s="38" t="n"/>
       <c r="W253" s="37" t="n"/>
+      <c r="X253" s="36" t="n"/>
     </row>
     <row r="254" ht="28" customHeight="1">
       <c r="A254" s="36" t="n"/>
@@ -16584,6 +16842,7 @@
       <c r="U254" s="39" t="n"/>
       <c r="V254" s="38" t="n"/>
       <c r="W254" s="37" t="n"/>
+      <c r="X254" s="36" t="n"/>
     </row>
     <row r="255" ht="28" customHeight="1">
       <c r="A255" s="36" t="n"/>
@@ -16609,6 +16868,7 @@
       <c r="U255" s="39" t="n"/>
       <c r="V255" s="38" t="n"/>
       <c r="W255" s="37" t="n"/>
+      <c r="X255" s="36" t="n"/>
     </row>
     <row r="256" ht="28" customHeight="1">
       <c r="A256" s="36" t="n"/>
@@ -16634,6 +16894,7 @@
       <c r="U256" s="39" t="n"/>
       <c r="V256" s="38" t="n"/>
       <c r="W256" s="37" t="n"/>
+      <c r="X256" s="36" t="n"/>
     </row>
     <row r="257" ht="28" customHeight="1">
       <c r="A257" s="36" t="n"/>
@@ -16659,6 +16920,7 @@
       <c r="U257" s="39" t="n"/>
       <c r="V257" s="38" t="n"/>
       <c r="W257" s="37" t="n"/>
+      <c r="X257" s="36" t="n"/>
     </row>
     <row r="258" ht="28" customHeight="1">
       <c r="A258" s="36" t="n"/>
@@ -16684,6 +16946,7 @@
       <c r="U258" s="39" t="n"/>
       <c r="V258" s="38" t="n"/>
       <c r="W258" s="37" t="n"/>
+      <c r="X258" s="36" t="n"/>
     </row>
     <row r="259" ht="28" customHeight="1">
       <c r="A259" s="36" t="n"/>
@@ -16709,6 +16972,7 @@
       <c r="U259" s="39" t="n"/>
       <c r="V259" s="38" t="n"/>
       <c r="W259" s="37" t="n"/>
+      <c r="X259" s="36" t="n"/>
     </row>
     <row r="260" ht="28" customHeight="1">
       <c r="A260" s="36" t="n"/>
@@ -16734,6 +16998,7 @@
       <c r="U260" s="39" t="n"/>
       <c r="V260" s="38" t="n"/>
       <c r="W260" s="37" t="n"/>
+      <c r="X260" s="36" t="n"/>
     </row>
     <row r="261" ht="28" customHeight="1">
       <c r="A261" s="36" t="n"/>
@@ -16759,6 +17024,7 @@
       <c r="U261" s="39" t="n"/>
       <c r="V261" s="38" t="n"/>
       <c r="W261" s="37" t="n"/>
+      <c r="X261" s="36" t="n"/>
     </row>
     <row r="262" ht="28" customHeight="1">
       <c r="A262" s="36" t="n"/>
@@ -16784,6 +17050,7 @@
       <c r="U262" s="39" t="n"/>
       <c r="V262" s="38" t="n"/>
       <c r="W262" s="37" t="n"/>
+      <c r="X262" s="36" t="n"/>
     </row>
     <row r="263" ht="28" customHeight="1">
       <c r="A263" s="36" t="n"/>
@@ -16809,6 +17076,7 @@
       <c r="U263" s="39" t="n"/>
       <c r="V263" s="38" t="n"/>
       <c r="W263" s="37" t="n"/>
+      <c r="X263" s="36" t="n"/>
     </row>
     <row r="264" ht="28" customHeight="1">
       <c r="A264" s="36" t="n"/>
@@ -16834,6 +17102,7 @@
       <c r="U264" s="39" t="n"/>
       <c r="V264" s="38" t="n"/>
       <c r="W264" s="37" t="n"/>
+      <c r="X264" s="36" t="n"/>
     </row>
     <row r="265" ht="28" customHeight="1">
       <c r="A265" s="36" t="n"/>
@@ -16859,6 +17128,7 @@
       <c r="U265" s="39" t="n"/>
       <c r="V265" s="38" t="n"/>
       <c r="W265" s="37" t="n"/>
+      <c r="X265" s="36" t="n"/>
     </row>
     <row r="266" ht="28" customHeight="1">
       <c r="A266" s="36" t="n"/>
@@ -16884,6 +17154,7 @@
       <c r="U266" s="39" t="n"/>
       <c r="V266" s="38" t="n"/>
       <c r="W266" s="37" t="n"/>
+      <c r="X266" s="36" t="n"/>
     </row>
     <row r="267" ht="28" customHeight="1">
       <c r="A267" s="36" t="n"/>
@@ -16909,6 +17180,7 @@
       <c r="U267" s="39" t="n"/>
       <c r="V267" s="38" t="n"/>
       <c r="W267" s="37" t="n"/>
+      <c r="X267" s="36" t="n"/>
     </row>
     <row r="268" ht="28" customHeight="1">
       <c r="A268" s="36" t="n"/>
@@ -16934,6 +17206,7 @@
       <c r="U268" s="39" t="n"/>
       <c r="V268" s="38" t="n"/>
       <c r="W268" s="37" t="n"/>
+      <c r="X268" s="36" t="n"/>
     </row>
     <row r="269" ht="28" customHeight="1">
       <c r="A269" s="36" t="n"/>
@@ -16959,6 +17232,7 @@
       <c r="U269" s="39" t="n"/>
       <c r="V269" s="38" t="n"/>
       <c r="W269" s="37" t="n"/>
+      <c r="X269" s="36" t="n"/>
     </row>
     <row r="270" ht="28" customHeight="1">
       <c r="A270" s="36" t="n"/>
@@ -16984,6 +17258,7 @@
       <c r="U270" s="39" t="n"/>
       <c r="V270" s="38" t="n"/>
       <c r="W270" s="37" t="n"/>
+      <c r="X270" s="36" t="n"/>
     </row>
     <row r="271" ht="28" customHeight="1">
       <c r="A271" s="36" t="n"/>
@@ -17009,6 +17284,7 @@
       <c r="U271" s="39" t="n"/>
       <c r="V271" s="38" t="n"/>
       <c r="W271" s="37" t="n"/>
+      <c r="X271" s="36" t="n"/>
     </row>
     <row r="272" ht="28" customHeight="1">
       <c r="A272" s="36" t="n"/>
@@ -17034,6 +17310,7 @@
       <c r="U272" s="39" t="n"/>
       <c r="V272" s="38" t="n"/>
       <c r="W272" s="37" t="n"/>
+      <c r="X272" s="36" t="n"/>
     </row>
     <row r="273" ht="28" customHeight="1">
       <c r="A273" s="36" t="n"/>
@@ -17059,6 +17336,7 @@
       <c r="U273" s="39" t="n"/>
       <c r="V273" s="38" t="n"/>
       <c r="W273" s="37" t="n"/>
+      <c r="X273" s="36" t="n"/>
     </row>
     <row r="274" ht="28" customHeight="1">
       <c r="A274" s="36" t="n"/>
@@ -17084,6 +17362,7 @@
       <c r="U274" s="39" t="n"/>
       <c r="V274" s="38" t="n"/>
       <c r="W274" s="37" t="n"/>
+      <c r="X274" s="36" t="n"/>
     </row>
     <row r="275" ht="28" customHeight="1">
       <c r="A275" s="36" t="n"/>
@@ -17109,6 +17388,7 @@
       <c r="U275" s="39" t="n"/>
       <c r="V275" s="38" t="n"/>
       <c r="W275" s="37" t="n"/>
+      <c r="X275" s="36" t="n"/>
     </row>
     <row r="276" ht="28" customHeight="1">
       <c r="A276" s="36" t="n"/>
@@ -17134,6 +17414,7 @@
       <c r="U276" s="39" t="n"/>
       <c r="V276" s="38" t="n"/>
       <c r="W276" s="37" t="n"/>
+      <c r="X276" s="36" t="n"/>
     </row>
     <row r="277" ht="28" customHeight="1">
       <c r="A277" s="36" t="n"/>
@@ -17159,6 +17440,7 @@
       <c r="U277" s="39" t="n"/>
       <c r="V277" s="38" t="n"/>
       <c r="W277" s="37" t="n"/>
+      <c r="X277" s="36" t="n"/>
     </row>
     <row r="278" ht="28" customHeight="1">
       <c r="A278" s="36" t="n"/>
@@ -17184,6 +17466,7 @@
       <c r="U278" s="39" t="n"/>
       <c r="V278" s="38" t="n"/>
       <c r="W278" s="37" t="n"/>
+      <c r="X278" s="36" t="n"/>
     </row>
     <row r="279" ht="28" customHeight="1">
       <c r="A279" s="36" t="n"/>
@@ -17209,6 +17492,7 @@
       <c r="U279" s="39" t="n"/>
       <c r="V279" s="38" t="n"/>
       <c r="W279" s="37" t="n"/>
+      <c r="X279" s="36" t="n"/>
     </row>
     <row r="280" ht="28" customHeight="1">
       <c r="A280" s="36" t="n"/>
@@ -17234,6 +17518,7 @@
       <c r="U280" s="39" t="n"/>
       <c r="V280" s="38" t="n"/>
       <c r="W280" s="37" t="n"/>
+      <c r="X280" s="36" t="n"/>
     </row>
     <row r="281" ht="28" customHeight="1">
       <c r="A281" s="36" t="n"/>
@@ -17259,6 +17544,7 @@
       <c r="U281" s="39" t="n"/>
       <c r="V281" s="38" t="n"/>
       <c r="W281" s="37" t="n"/>
+      <c r="X281" s="36" t="n"/>
     </row>
     <row r="282" ht="28" customHeight="1">
       <c r="A282" s="36" t="n"/>
@@ -17284,6 +17570,7 @@
       <c r="U282" s="39" t="n"/>
       <c r="V282" s="38" t="n"/>
       <c r="W282" s="37" t="n"/>
+      <c r="X282" s="36" t="n"/>
     </row>
     <row r="283" ht="28" customHeight="1">
       <c r="A283" s="36" t="n"/>
@@ -17309,6 +17596,7 @@
       <c r="U283" s="39" t="n"/>
       <c r="V283" s="38" t="n"/>
       <c r="W283" s="37" t="n"/>
+      <c r="X283" s="36" t="n"/>
     </row>
     <row r="284" ht="28" customHeight="1">
       <c r="A284" s="36" t="n"/>
@@ -17334,6 +17622,7 @@
       <c r="U284" s="39" t="n"/>
       <c r="V284" s="38" t="n"/>
       <c r="W284" s="37" t="n"/>
+      <c r="X284" s="36" t="n"/>
     </row>
     <row r="285" ht="28" customHeight="1">
       <c r="A285" s="36" t="n"/>
@@ -17359,6 +17648,7 @@
       <c r="U285" s="39" t="n"/>
       <c r="V285" s="38" t="n"/>
       <c r="W285" s="37" t="n"/>
+      <c r="X285" s="36" t="n"/>
     </row>
     <row r="286" ht="28" customHeight="1">
       <c r="A286" s="36" t="n"/>
@@ -17384,6 +17674,7 @@
       <c r="U286" s="39" t="n"/>
       <c r="V286" s="38" t="n"/>
       <c r="W286" s="37" t="n"/>
+      <c r="X286" s="36" t="n"/>
     </row>
     <row r="287" ht="28" customHeight="1">
       <c r="A287" s="36" t="n"/>
@@ -17409,6 +17700,7 @@
       <c r="U287" s="39" t="n"/>
       <c r="V287" s="38" t="n"/>
       <c r="W287" s="37" t="n"/>
+      <c r="X287" s="36" t="n"/>
     </row>
     <row r="288" ht="28" customHeight="1">
       <c r="A288" s="36" t="n"/>
@@ -17434,6 +17726,7 @@
       <c r="U288" s="39" t="n"/>
       <c r="V288" s="38" t="n"/>
       <c r="W288" s="37" t="n"/>
+      <c r="X288" s="36" t="n"/>
     </row>
     <row r="289" ht="28" customHeight="1">
       <c r="A289" s="36" t="n"/>
@@ -17459,6 +17752,7 @@
       <c r="U289" s="39" t="n"/>
       <c r="V289" s="38" t="n"/>
       <c r="W289" s="37" t="n"/>
+      <c r="X289" s="36" t="n"/>
     </row>
     <row r="290" ht="28" customHeight="1">
       <c r="A290" s="36" t="n"/>
@@ -17484,6 +17778,7 @@
       <c r="U290" s="39" t="n"/>
       <c r="V290" s="38" t="n"/>
       <c r="W290" s="37" t="n"/>
+      <c r="X290" s="36" t="n"/>
     </row>
     <row r="291" ht="28" customHeight="1">
       <c r="A291" s="36" t="n"/>
@@ -17509,6 +17804,7 @@
       <c r="U291" s="39" t="n"/>
       <c r="V291" s="38" t="n"/>
       <c r="W291" s="37" t="n"/>
+      <c r="X291" s="36" t="n"/>
     </row>
     <row r="292" ht="28" customHeight="1">
       <c r="A292" s="36" t="n"/>
@@ -17534,6 +17830,7 @@
       <c r="U292" s="39" t="n"/>
       <c r="V292" s="38" t="n"/>
       <c r="W292" s="37" t="n"/>
+      <c r="X292" s="36" t="n"/>
     </row>
     <row r="293" ht="28" customHeight="1">
       <c r="A293" s="36" t="n"/>
@@ -17559,6 +17856,7 @@
       <c r="U293" s="39" t="n"/>
       <c r="V293" s="38" t="n"/>
       <c r="W293" s="37" t="n"/>
+      <c r="X293" s="36" t="n"/>
     </row>
     <row r="294" ht="28" customHeight="1">
       <c r="A294" s="36" t="n"/>
@@ -17584,6 +17882,7 @@
       <c r="U294" s="39" t="n"/>
       <c r="V294" s="38" t="n"/>
       <c r="W294" s="37" t="n"/>
+      <c r="X294" s="36" t="n"/>
     </row>
     <row r="295" ht="28" customHeight="1">
       <c r="A295" s="36" t="n"/>
@@ -17609,6 +17908,7 @@
       <c r="U295" s="39" t="n"/>
       <c r="V295" s="38" t="n"/>
       <c r="W295" s="37" t="n"/>
+      <c r="X295" s="36" t="n"/>
     </row>
     <row r="296" ht="28" customHeight="1">
       <c r="A296" s="36" t="n"/>
@@ -17634,6 +17934,7 @@
       <c r="U296" s="39" t="n"/>
       <c r="V296" s="38" t="n"/>
       <c r="W296" s="37" t="n"/>
+      <c r="X296" s="36" t="n"/>
     </row>
     <row r="297" ht="28" customHeight="1">
       <c r="A297" s="36" t="n"/>
@@ -17659,6 +17960,7 @@
       <c r="U297" s="39" t="n"/>
       <c r="V297" s="38" t="n"/>
       <c r="W297" s="37" t="n"/>
+      <c r="X297" s="36" t="n"/>
     </row>
     <row r="298" ht="28" customHeight="1">
       <c r="A298" s="36" t="n"/>
@@ -17684,6 +17986,7 @@
       <c r="U298" s="39" t="n"/>
       <c r="V298" s="38" t="n"/>
       <c r="W298" s="37" t="n"/>
+      <c r="X298" s="36" t="n"/>
     </row>
     <row r="299" ht="28" customHeight="1">
       <c r="A299" s="36" t="n"/>
@@ -17709,6 +18012,7 @@
       <c r="U299" s="39" t="n"/>
       <c r="V299" s="38" t="n"/>
       <c r="W299" s="37" t="n"/>
+      <c r="X299" s="36" t="n"/>
     </row>
     <row r="300" ht="28" customHeight="1">
       <c r="A300" s="36" t="n"/>
@@ -17734,6 +18038,7 @@
       <c r="U300" s="39" t="n"/>
       <c r="V300" s="38" t="n"/>
       <c r="W300" s="37" t="n"/>
+      <c r="X300" s="36" t="n"/>
     </row>
     <row r="301" ht="28" customHeight="1">
       <c r="A301" s="36" t="n"/>
@@ -17759,6 +18064,7 @@
       <c r="U301" s="39" t="n"/>
       <c r="V301" s="38" t="n"/>
       <c r="W301" s="37" t="n"/>
+      <c r="X301" s="36" t="n"/>
     </row>
     <row r="302" ht="28" customHeight="1">
       <c r="A302" s="36" t="n"/>
@@ -17784,6 +18090,7 @@
       <c r="U302" s="39" t="n"/>
       <c r="V302" s="38" t="n"/>
       <c r="W302" s="37" t="n"/>
+      <c r="X302" s="36" t="n"/>
     </row>
     <row r="303" ht="28" customHeight="1">
       <c r="A303" s="36" t="n"/>
@@ -17809,9 +18116,10 @@
       <c r="U303" s="39" t="n"/>
       <c r="V303" s="38" t="n"/>
       <c r="W303" s="37" t="n"/>
+      <c r="X303" s="36" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:W303"/>
+  <autoFilter ref="A3:X303"/>
   <conditionalFormatting sqref="G4:G303">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="3">
       <formula>"مفتوح"</formula>
@@ -17820,7 +18128,7 @@
       <formula>"مقفّل"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:W303">
+  <conditionalFormatting sqref="A4:X303">
     <cfRule type="expression" priority="3" dxfId="2">
       <formula>AND(MOD(ROW(),2)=1,$A4&lt;&gt;"")</formula>
     </cfRule>
@@ -17842,7 +18150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J303"/>
+  <dimension ref="A1:K303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -17855,6 +18163,7 @@
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col hidden="1" width="12" customWidth="1" min="10" max="10"/>
+    <col hidden="1" width="15" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="44" customHeight="1">
@@ -17872,6 +18181,7 @@
       <c r="H1" s="48" t="n"/>
       <c r="I1" s="48" t="n"/>
       <c r="J1" s="48" t="n"/>
+      <c r="K1" s="48" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -17888,6 +18198,7 @@
       <c r="H2" s="33" t="n"/>
       <c r="I2" s="33" t="n"/>
       <c r="J2" s="33" t="n"/>
+      <c r="K2" s="33" t="n"/>
     </row>
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
@@ -17938,6 +18249,11 @@
       <c r="J3" s="35" t="inlineStr">
         <is>
           <t>الإصدار</t>
+        </is>
+      </c>
+      <c r="K3" s="34" t="inlineStr">
+        <is>
+          <t>مفتاح عدم التكرار</t>
         </is>
       </c>
     </row>
@@ -17952,6 +18268,7 @@
       <c r="H4" s="39" t="n"/>
       <c r="I4" s="38" t="n"/>
       <c r="J4" s="37" t="n"/>
+      <c r="K4" s="36" t="n"/>
     </row>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="36" t="n"/>
@@ -17964,6 +18281,7 @@
       <c r="H5" s="39" t="n"/>
       <c r="I5" s="38" t="n"/>
       <c r="J5" s="37" t="n"/>
+      <c r="K5" s="36" t="n"/>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="36" t="n"/>
@@ -17976,6 +18294,7 @@
       <c r="H6" s="39" t="n"/>
       <c r="I6" s="38" t="n"/>
       <c r="J6" s="37" t="n"/>
+      <c r="K6" s="36" t="n"/>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="36" t="n"/>
@@ -17988,6 +18307,7 @@
       <c r="H7" s="39" t="n"/>
       <c r="I7" s="38" t="n"/>
       <c r="J7" s="37" t="n"/>
+      <c r="K7" s="36" t="n"/>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="36" t="n"/>
@@ -18000,6 +18320,7 @@
       <c r="H8" s="39" t="n"/>
       <c r="I8" s="38" t="n"/>
       <c r="J8" s="37" t="n"/>
+      <c r="K8" s="36" t="n"/>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="36" t="n"/>
@@ -18012,6 +18333,7 @@
       <c r="H9" s="39" t="n"/>
       <c r="I9" s="38" t="n"/>
       <c r="J9" s="37" t="n"/>
+      <c r="K9" s="36" t="n"/>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="36" t="n"/>
@@ -18024,6 +18346,7 @@
       <c r="H10" s="39" t="n"/>
       <c r="I10" s="38" t="n"/>
       <c r="J10" s="37" t="n"/>
+      <c r="K10" s="36" t="n"/>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="36" t="n"/>
@@ -18036,6 +18359,7 @@
       <c r="H11" s="39" t="n"/>
       <c r="I11" s="38" t="n"/>
       <c r="J11" s="37" t="n"/>
+      <c r="K11" s="36" t="n"/>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="36" t="n"/>
@@ -18048,6 +18372,7 @@
       <c r="H12" s="39" t="n"/>
       <c r="I12" s="38" t="n"/>
       <c r="J12" s="37" t="n"/>
+      <c r="K12" s="36" t="n"/>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="36" t="n"/>
@@ -18060,6 +18385,7 @@
       <c r="H13" s="39" t="n"/>
       <c r="I13" s="38" t="n"/>
       <c r="J13" s="37" t="n"/>
+      <c r="K13" s="36" t="n"/>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="36" t="n"/>
@@ -18072,6 +18398,7 @@
       <c r="H14" s="39" t="n"/>
       <c r="I14" s="38" t="n"/>
       <c r="J14" s="37" t="n"/>
+      <c r="K14" s="36" t="n"/>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="36" t="n"/>
@@ -18084,6 +18411,7 @@
       <c r="H15" s="39" t="n"/>
       <c r="I15" s="38" t="n"/>
       <c r="J15" s="37" t="n"/>
+      <c r="K15" s="36" t="n"/>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="36" t="n"/>
@@ -18096,6 +18424,7 @@
       <c r="H16" s="39" t="n"/>
       <c r="I16" s="38" t="n"/>
       <c r="J16" s="37" t="n"/>
+      <c r="K16" s="36" t="n"/>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="36" t="n"/>
@@ -18108,6 +18437,7 @@
       <c r="H17" s="39" t="n"/>
       <c r="I17" s="38" t="n"/>
       <c r="J17" s="37" t="n"/>
+      <c r="K17" s="36" t="n"/>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="36" t="n"/>
@@ -18120,6 +18450,7 @@
       <c r="H18" s="39" t="n"/>
       <c r="I18" s="38" t="n"/>
       <c r="J18" s="37" t="n"/>
+      <c r="K18" s="36" t="n"/>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="36" t="n"/>
@@ -18132,6 +18463,7 @@
       <c r="H19" s="39" t="n"/>
       <c r="I19" s="38" t="n"/>
       <c r="J19" s="37" t="n"/>
+      <c r="K19" s="36" t="n"/>
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="36" t="n"/>
@@ -18144,6 +18476,7 @@
       <c r="H20" s="39" t="n"/>
       <c r="I20" s="38" t="n"/>
       <c r="J20" s="37" t="n"/>
+      <c r="K20" s="36" t="n"/>
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="36" t="n"/>
@@ -18156,6 +18489,7 @@
       <c r="H21" s="39" t="n"/>
       <c r="I21" s="38" t="n"/>
       <c r="J21" s="37" t="n"/>
+      <c r="K21" s="36" t="n"/>
     </row>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="36" t="n"/>
@@ -18168,6 +18502,7 @@
       <c r="H22" s="39" t="n"/>
       <c r="I22" s="38" t="n"/>
       <c r="J22" s="37" t="n"/>
+      <c r="K22" s="36" t="n"/>
     </row>
     <row r="23" ht="28" customHeight="1">
       <c r="A23" s="36" t="n"/>
@@ -18180,6 +18515,7 @@
       <c r="H23" s="39" t="n"/>
       <c r="I23" s="38" t="n"/>
       <c r="J23" s="37" t="n"/>
+      <c r="K23" s="36" t="n"/>
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="36" t="n"/>
@@ -18192,6 +18528,7 @@
       <c r="H24" s="39" t="n"/>
       <c r="I24" s="38" t="n"/>
       <c r="J24" s="37" t="n"/>
+      <c r="K24" s="36" t="n"/>
     </row>
     <row r="25" ht="28" customHeight="1">
       <c r="A25" s="36" t="n"/>
@@ -18204,6 +18541,7 @@
       <c r="H25" s="39" t="n"/>
       <c r="I25" s="38" t="n"/>
       <c r="J25" s="37" t="n"/>
+      <c r="K25" s="36" t="n"/>
     </row>
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="36" t="n"/>
@@ -18216,6 +18554,7 @@
       <c r="H26" s="39" t="n"/>
       <c r="I26" s="38" t="n"/>
       <c r="J26" s="37" t="n"/>
+      <c r="K26" s="36" t="n"/>
     </row>
     <row r="27" ht="28" customHeight="1">
       <c r="A27" s="36" t="n"/>
@@ -18228,6 +18567,7 @@
       <c r="H27" s="39" t="n"/>
       <c r="I27" s="38" t="n"/>
       <c r="J27" s="37" t="n"/>
+      <c r="K27" s="36" t="n"/>
     </row>
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="36" t="n"/>
@@ -18240,6 +18580,7 @@
       <c r="H28" s="39" t="n"/>
       <c r="I28" s="38" t="n"/>
       <c r="J28" s="37" t="n"/>
+      <c r="K28" s="36" t="n"/>
     </row>
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="36" t="n"/>
@@ -18252,6 +18593,7 @@
       <c r="H29" s="39" t="n"/>
       <c r="I29" s="38" t="n"/>
       <c r="J29" s="37" t="n"/>
+      <c r="K29" s="36" t="n"/>
     </row>
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="36" t="n"/>
@@ -18264,6 +18606,7 @@
       <c r="H30" s="39" t="n"/>
       <c r="I30" s="38" t="n"/>
       <c r="J30" s="37" t="n"/>
+      <c r="K30" s="36" t="n"/>
     </row>
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="36" t="n"/>
@@ -18276,6 +18619,7 @@
       <c r="H31" s="39" t="n"/>
       <c r="I31" s="38" t="n"/>
       <c r="J31" s="37" t="n"/>
+      <c r="K31" s="36" t="n"/>
     </row>
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="36" t="n"/>
@@ -18288,6 +18632,7 @@
       <c r="H32" s="39" t="n"/>
       <c r="I32" s="38" t="n"/>
       <c r="J32" s="37" t="n"/>
+      <c r="K32" s="36" t="n"/>
     </row>
     <row r="33" ht="28" customHeight="1">
       <c r="A33" s="36" t="n"/>
@@ -18300,6 +18645,7 @@
       <c r="H33" s="39" t="n"/>
       <c r="I33" s="38" t="n"/>
       <c r="J33" s="37" t="n"/>
+      <c r="K33" s="36" t="n"/>
     </row>
     <row r="34" ht="28" customHeight="1">
       <c r="A34" s="36" t="n"/>
@@ -18312,6 +18658,7 @@
       <c r="H34" s="39" t="n"/>
       <c r="I34" s="38" t="n"/>
       <c r="J34" s="37" t="n"/>
+      <c r="K34" s="36" t="n"/>
     </row>
     <row r="35" ht="28" customHeight="1">
       <c r="A35" s="36" t="n"/>
@@ -18324,6 +18671,7 @@
       <c r="H35" s="39" t="n"/>
       <c r="I35" s="38" t="n"/>
       <c r="J35" s="37" t="n"/>
+      <c r="K35" s="36" t="n"/>
     </row>
     <row r="36" ht="28" customHeight="1">
       <c r="A36" s="36" t="n"/>
@@ -18336,6 +18684,7 @@
       <c r="H36" s="39" t="n"/>
       <c r="I36" s="38" t="n"/>
       <c r="J36" s="37" t="n"/>
+      <c r="K36" s="36" t="n"/>
     </row>
     <row r="37" ht="28" customHeight="1">
       <c r="A37" s="36" t="n"/>
@@ -18348,6 +18697,7 @@
       <c r="H37" s="39" t="n"/>
       <c r="I37" s="38" t="n"/>
       <c r="J37" s="37" t="n"/>
+      <c r="K37" s="36" t="n"/>
     </row>
     <row r="38" ht="28" customHeight="1">
       <c r="A38" s="36" t="n"/>
@@ -18360,6 +18710,7 @@
       <c r="H38" s="39" t="n"/>
       <c r="I38" s="38" t="n"/>
       <c r="J38" s="37" t="n"/>
+      <c r="K38" s="36" t="n"/>
     </row>
     <row r="39" ht="28" customHeight="1">
       <c r="A39" s="36" t="n"/>
@@ -18372,6 +18723,7 @@
       <c r="H39" s="39" t="n"/>
       <c r="I39" s="38" t="n"/>
       <c r="J39" s="37" t="n"/>
+      <c r="K39" s="36" t="n"/>
     </row>
     <row r="40" ht="28" customHeight="1">
       <c r="A40" s="36" t="n"/>
@@ -18384,6 +18736,7 @@
       <c r="H40" s="39" t="n"/>
       <c r="I40" s="38" t="n"/>
       <c r="J40" s="37" t="n"/>
+      <c r="K40" s="36" t="n"/>
     </row>
     <row r="41" ht="28" customHeight="1">
       <c r="A41" s="36" t="n"/>
@@ -18396,6 +18749,7 @@
       <c r="H41" s="39" t="n"/>
       <c r="I41" s="38" t="n"/>
       <c r="J41" s="37" t="n"/>
+      <c r="K41" s="36" t="n"/>
     </row>
     <row r="42" ht="28" customHeight="1">
       <c r="A42" s="36" t="n"/>
@@ -18408,6 +18762,7 @@
       <c r="H42" s="39" t="n"/>
       <c r="I42" s="38" t="n"/>
       <c r="J42" s="37" t="n"/>
+      <c r="K42" s="36" t="n"/>
     </row>
     <row r="43" ht="28" customHeight="1">
       <c r="A43" s="36" t="n"/>
@@ -18420,6 +18775,7 @@
       <c r="H43" s="39" t="n"/>
       <c r="I43" s="38" t="n"/>
       <c r="J43" s="37" t="n"/>
+      <c r="K43" s="36" t="n"/>
     </row>
     <row r="44" ht="28" customHeight="1">
       <c r="A44" s="36" t="n"/>
@@ -18432,6 +18788,7 @@
       <c r="H44" s="39" t="n"/>
       <c r="I44" s="38" t="n"/>
       <c r="J44" s="37" t="n"/>
+      <c r="K44" s="36" t="n"/>
     </row>
     <row r="45" ht="28" customHeight="1">
       <c r="A45" s="36" t="n"/>
@@ -18444,6 +18801,7 @@
       <c r="H45" s="39" t="n"/>
       <c r="I45" s="38" t="n"/>
       <c r="J45" s="37" t="n"/>
+      <c r="K45" s="36" t="n"/>
     </row>
     <row r="46" ht="28" customHeight="1">
       <c r="A46" s="36" t="n"/>
@@ -18456,6 +18814,7 @@
       <c r="H46" s="39" t="n"/>
       <c r="I46" s="38" t="n"/>
       <c r="J46" s="37" t="n"/>
+      <c r="K46" s="36" t="n"/>
     </row>
     <row r="47" ht="28" customHeight="1">
       <c r="A47" s="36" t="n"/>
@@ -18468,6 +18827,7 @@
       <c r="H47" s="39" t="n"/>
       <c r="I47" s="38" t="n"/>
       <c r="J47" s="37" t="n"/>
+      <c r="K47" s="36" t="n"/>
     </row>
     <row r="48" ht="28" customHeight="1">
       <c r="A48" s="36" t="n"/>
@@ -18480,6 +18840,7 @@
       <c r="H48" s="39" t="n"/>
       <c r="I48" s="38" t="n"/>
       <c r="J48" s="37" t="n"/>
+      <c r="K48" s="36" t="n"/>
     </row>
     <row r="49" ht="28" customHeight="1">
       <c r="A49" s="36" t="n"/>
@@ -18492,6 +18853,7 @@
       <c r="H49" s="39" t="n"/>
       <c r="I49" s="38" t="n"/>
       <c r="J49" s="37" t="n"/>
+      <c r="K49" s="36" t="n"/>
     </row>
     <row r="50" ht="28" customHeight="1">
       <c r="A50" s="36" t="n"/>
@@ -18504,6 +18866,7 @@
       <c r="H50" s="39" t="n"/>
       <c r="I50" s="38" t="n"/>
       <c r="J50" s="37" t="n"/>
+      <c r="K50" s="36" t="n"/>
     </row>
     <row r="51" ht="28" customHeight="1">
       <c r="A51" s="36" t="n"/>
@@ -18516,6 +18879,7 @@
       <c r="H51" s="39" t="n"/>
       <c r="I51" s="38" t="n"/>
       <c r="J51" s="37" t="n"/>
+      <c r="K51" s="36" t="n"/>
     </row>
     <row r="52" ht="28" customHeight="1">
       <c r="A52" s="36" t="n"/>
@@ -18528,6 +18892,7 @@
       <c r="H52" s="39" t="n"/>
       <c r="I52" s="38" t="n"/>
       <c r="J52" s="37" t="n"/>
+      <c r="K52" s="36" t="n"/>
     </row>
     <row r="53" ht="28" customHeight="1">
       <c r="A53" s="36" t="n"/>
@@ -18540,6 +18905,7 @@
       <c r="H53" s="39" t="n"/>
       <c r="I53" s="38" t="n"/>
       <c r="J53" s="37" t="n"/>
+      <c r="K53" s="36" t="n"/>
     </row>
     <row r="54" ht="28" customHeight="1">
       <c r="A54" s="36" t="n"/>
@@ -18552,6 +18918,7 @@
       <c r="H54" s="39" t="n"/>
       <c r="I54" s="38" t="n"/>
       <c r="J54" s="37" t="n"/>
+      <c r="K54" s="36" t="n"/>
     </row>
     <row r="55" ht="28" customHeight="1">
       <c r="A55" s="36" t="n"/>
@@ -18564,6 +18931,7 @@
       <c r="H55" s="39" t="n"/>
       <c r="I55" s="38" t="n"/>
       <c r="J55" s="37" t="n"/>
+      <c r="K55" s="36" t="n"/>
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="36" t="n"/>
@@ -18576,6 +18944,7 @@
       <c r="H56" s="39" t="n"/>
       <c r="I56" s="38" t="n"/>
       <c r="J56" s="37" t="n"/>
+      <c r="K56" s="36" t="n"/>
     </row>
     <row r="57" ht="28" customHeight="1">
       <c r="A57" s="36" t="n"/>
@@ -18588,6 +18957,7 @@
       <c r="H57" s="39" t="n"/>
       <c r="I57" s="38" t="n"/>
       <c r="J57" s="37" t="n"/>
+      <c r="K57" s="36" t="n"/>
     </row>
     <row r="58" ht="28" customHeight="1">
       <c r="A58" s="36" t="n"/>
@@ -18600,6 +18970,7 @@
       <c r="H58" s="39" t="n"/>
       <c r="I58" s="38" t="n"/>
       <c r="J58" s="37" t="n"/>
+      <c r="K58" s="36" t="n"/>
     </row>
     <row r="59" ht="28" customHeight="1">
       <c r="A59" s="36" t="n"/>
@@ -18612,6 +18983,7 @@
       <c r="H59" s="39" t="n"/>
       <c r="I59" s="38" t="n"/>
       <c r="J59" s="37" t="n"/>
+      <c r="K59" s="36" t="n"/>
     </row>
     <row r="60" ht="28" customHeight="1">
       <c r="A60" s="36" t="n"/>
@@ -18624,6 +18996,7 @@
       <c r="H60" s="39" t="n"/>
       <c r="I60" s="38" t="n"/>
       <c r="J60" s="37" t="n"/>
+      <c r="K60" s="36" t="n"/>
     </row>
     <row r="61" ht="28" customHeight="1">
       <c r="A61" s="36" t="n"/>
@@ -18636,6 +19009,7 @@
       <c r="H61" s="39" t="n"/>
       <c r="I61" s="38" t="n"/>
       <c r="J61" s="37" t="n"/>
+      <c r="K61" s="36" t="n"/>
     </row>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="36" t="n"/>
@@ -18648,6 +19022,7 @@
       <c r="H62" s="39" t="n"/>
       <c r="I62" s="38" t="n"/>
       <c r="J62" s="37" t="n"/>
+      <c r="K62" s="36" t="n"/>
     </row>
     <row r="63" ht="28" customHeight="1">
       <c r="A63" s="36" t="n"/>
@@ -18660,6 +19035,7 @@
       <c r="H63" s="39" t="n"/>
       <c r="I63" s="38" t="n"/>
       <c r="J63" s="37" t="n"/>
+      <c r="K63" s="36" t="n"/>
     </row>
     <row r="64" ht="28" customHeight="1">
       <c r="A64" s="36" t="n"/>
@@ -18672,6 +19048,7 @@
       <c r="H64" s="39" t="n"/>
       <c r="I64" s="38" t="n"/>
       <c r="J64" s="37" t="n"/>
+      <c r="K64" s="36" t="n"/>
     </row>
     <row r="65" ht="28" customHeight="1">
       <c r="A65" s="36" t="n"/>
@@ -18684,6 +19061,7 @@
       <c r="H65" s="39" t="n"/>
       <c r="I65" s="38" t="n"/>
       <c r="J65" s="37" t="n"/>
+      <c r="K65" s="36" t="n"/>
     </row>
     <row r="66" ht="28" customHeight="1">
       <c r="A66" s="36" t="n"/>
@@ -18696,6 +19074,7 @@
       <c r="H66" s="39" t="n"/>
       <c r="I66" s="38" t="n"/>
       <c r="J66" s="37" t="n"/>
+      <c r="K66" s="36" t="n"/>
     </row>
     <row r="67" ht="28" customHeight="1">
       <c r="A67" s="36" t="n"/>
@@ -18708,6 +19087,7 @@
       <c r="H67" s="39" t="n"/>
       <c r="I67" s="38" t="n"/>
       <c r="J67" s="37" t="n"/>
+      <c r="K67" s="36" t="n"/>
     </row>
     <row r="68" ht="28" customHeight="1">
       <c r="A68" s="36" t="n"/>
@@ -18720,6 +19100,7 @@
       <c r="H68" s="39" t="n"/>
       <c r="I68" s="38" t="n"/>
       <c r="J68" s="37" t="n"/>
+      <c r="K68" s="36" t="n"/>
     </row>
     <row r="69" ht="28" customHeight="1">
       <c r="A69" s="36" t="n"/>
@@ -18732,6 +19113,7 @@
       <c r="H69" s="39" t="n"/>
       <c r="I69" s="38" t="n"/>
       <c r="J69" s="37" t="n"/>
+      <c r="K69" s="36" t="n"/>
     </row>
     <row r="70" ht="28" customHeight="1">
       <c r="A70" s="36" t="n"/>
@@ -18744,6 +19126,7 @@
       <c r="H70" s="39" t="n"/>
       <c r="I70" s="38" t="n"/>
       <c r="J70" s="37" t="n"/>
+      <c r="K70" s="36" t="n"/>
     </row>
     <row r="71" ht="28" customHeight="1">
       <c r="A71" s="36" t="n"/>
@@ -18756,6 +19139,7 @@
       <c r="H71" s="39" t="n"/>
       <c r="I71" s="38" t="n"/>
       <c r="J71" s="37" t="n"/>
+      <c r="K71" s="36" t="n"/>
     </row>
     <row r="72" ht="28" customHeight="1">
       <c r="A72" s="36" t="n"/>
@@ -18768,6 +19152,7 @@
       <c r="H72" s="39" t="n"/>
       <c r="I72" s="38" t="n"/>
       <c r="J72" s="37" t="n"/>
+      <c r="K72" s="36" t="n"/>
     </row>
     <row r="73" ht="28" customHeight="1">
       <c r="A73" s="36" t="n"/>
@@ -18780,6 +19165,7 @@
       <c r="H73" s="39" t="n"/>
       <c r="I73" s="38" t="n"/>
       <c r="J73" s="37" t="n"/>
+      <c r="K73" s="36" t="n"/>
     </row>
     <row r="74" ht="28" customHeight="1">
       <c r="A74" s="36" t="n"/>
@@ -18792,6 +19178,7 @@
       <c r="H74" s="39" t="n"/>
       <c r="I74" s="38" t="n"/>
       <c r="J74" s="37" t="n"/>
+      <c r="K74" s="36" t="n"/>
     </row>
     <row r="75" ht="28" customHeight="1">
       <c r="A75" s="36" t="n"/>
@@ -18804,6 +19191,7 @@
       <c r="H75" s="39" t="n"/>
       <c r="I75" s="38" t="n"/>
       <c r="J75" s="37" t="n"/>
+      <c r="K75" s="36" t="n"/>
     </row>
     <row r="76" ht="28" customHeight="1">
       <c r="A76" s="36" t="n"/>
@@ -18816,6 +19204,7 @@
       <c r="H76" s="39" t="n"/>
       <c r="I76" s="38" t="n"/>
       <c r="J76" s="37" t="n"/>
+      <c r="K76" s="36" t="n"/>
     </row>
     <row r="77" ht="28" customHeight="1">
       <c r="A77" s="36" t="n"/>
@@ -18828,6 +19217,7 @@
       <c r="H77" s="39" t="n"/>
       <c r="I77" s="38" t="n"/>
       <c r="J77" s="37" t="n"/>
+      <c r="K77" s="36" t="n"/>
     </row>
     <row r="78" ht="28" customHeight="1">
       <c r="A78" s="36" t="n"/>
@@ -18840,6 +19230,7 @@
       <c r="H78" s="39" t="n"/>
       <c r="I78" s="38" t="n"/>
       <c r="J78" s="37" t="n"/>
+      <c r="K78" s="36" t="n"/>
     </row>
     <row r="79" ht="28" customHeight="1">
       <c r="A79" s="36" t="n"/>
@@ -18852,6 +19243,7 @@
       <c r="H79" s="39" t="n"/>
       <c r="I79" s="38" t="n"/>
       <c r="J79" s="37" t="n"/>
+      <c r="K79" s="36" t="n"/>
     </row>
     <row r="80" ht="28" customHeight="1">
       <c r="A80" s="36" t="n"/>
@@ -18864,6 +19256,7 @@
       <c r="H80" s="39" t="n"/>
       <c r="I80" s="38" t="n"/>
       <c r="J80" s="37" t="n"/>
+      <c r="K80" s="36" t="n"/>
     </row>
     <row r="81" ht="28" customHeight="1">
       <c r="A81" s="36" t="n"/>
@@ -18876,6 +19269,7 @@
       <c r="H81" s="39" t="n"/>
       <c r="I81" s="38" t="n"/>
       <c r="J81" s="37" t="n"/>
+      <c r="K81" s="36" t="n"/>
     </row>
     <row r="82" ht="28" customHeight="1">
       <c r="A82" s="36" t="n"/>
@@ -18888,6 +19282,7 @@
       <c r="H82" s="39" t="n"/>
       <c r="I82" s="38" t="n"/>
       <c r="J82" s="37" t="n"/>
+      <c r="K82" s="36" t="n"/>
     </row>
     <row r="83" ht="28" customHeight="1">
       <c r="A83" s="36" t="n"/>
@@ -18900,6 +19295,7 @@
       <c r="H83" s="39" t="n"/>
       <c r="I83" s="38" t="n"/>
       <c r="J83" s="37" t="n"/>
+      <c r="K83" s="36" t="n"/>
     </row>
     <row r="84" ht="28" customHeight="1">
       <c r="A84" s="36" t="n"/>
@@ -18912,6 +19308,7 @@
       <c r="H84" s="39" t="n"/>
       <c r="I84" s="38" t="n"/>
       <c r="J84" s="37" t="n"/>
+      <c r="K84" s="36" t="n"/>
     </row>
     <row r="85" ht="28" customHeight="1">
       <c r="A85" s="36" t="n"/>
@@ -18924,6 +19321,7 @@
       <c r="H85" s="39" t="n"/>
       <c r="I85" s="38" t="n"/>
       <c r="J85" s="37" t="n"/>
+      <c r="K85" s="36" t="n"/>
     </row>
     <row r="86" ht="28" customHeight="1">
       <c r="A86" s="36" t="n"/>
@@ -18936,6 +19334,7 @@
       <c r="H86" s="39" t="n"/>
       <c r="I86" s="38" t="n"/>
       <c r="J86" s="37" t="n"/>
+      <c r="K86" s="36" t="n"/>
     </row>
     <row r="87" ht="28" customHeight="1">
       <c r="A87" s="36" t="n"/>
@@ -18948,6 +19347,7 @@
       <c r="H87" s="39" t="n"/>
       <c r="I87" s="38" t="n"/>
       <c r="J87" s="37" t="n"/>
+      <c r="K87" s="36" t="n"/>
     </row>
     <row r="88" ht="28" customHeight="1">
       <c r="A88" s="36" t="n"/>
@@ -18960,6 +19360,7 @@
       <c r="H88" s="39" t="n"/>
       <c r="I88" s="38" t="n"/>
       <c r="J88" s="37" t="n"/>
+      <c r="K88" s="36" t="n"/>
     </row>
     <row r="89" ht="28" customHeight="1">
       <c r="A89" s="36" t="n"/>
@@ -18972,6 +19373,7 @@
       <c r="H89" s="39" t="n"/>
       <c r="I89" s="38" t="n"/>
       <c r="J89" s="37" t="n"/>
+      <c r="K89" s="36" t="n"/>
     </row>
     <row r="90" ht="28" customHeight="1">
       <c r="A90" s="36" t="n"/>
@@ -18984,6 +19386,7 @@
       <c r="H90" s="39" t="n"/>
       <c r="I90" s="38" t="n"/>
       <c r="J90" s="37" t="n"/>
+      <c r="K90" s="36" t="n"/>
     </row>
     <row r="91" ht="28" customHeight="1">
       <c r="A91" s="36" t="n"/>
@@ -18996,6 +19399,7 @@
       <c r="H91" s="39" t="n"/>
       <c r="I91" s="38" t="n"/>
       <c r="J91" s="37" t="n"/>
+      <c r="K91" s="36" t="n"/>
     </row>
     <row r="92" ht="28" customHeight="1">
       <c r="A92" s="36" t="n"/>
@@ -19008,6 +19412,7 @@
       <c r="H92" s="39" t="n"/>
       <c r="I92" s="38" t="n"/>
       <c r="J92" s="37" t="n"/>
+      <c r="K92" s="36" t="n"/>
     </row>
     <row r="93" ht="28" customHeight="1">
       <c r="A93" s="36" t="n"/>
@@ -19020,6 +19425,7 @@
       <c r="H93" s="39" t="n"/>
       <c r="I93" s="38" t="n"/>
       <c r="J93" s="37" t="n"/>
+      <c r="K93" s="36" t="n"/>
     </row>
     <row r="94" ht="28" customHeight="1">
       <c r="A94" s="36" t="n"/>
@@ -19032,6 +19438,7 @@
       <c r="H94" s="39" t="n"/>
       <c r="I94" s="38" t="n"/>
       <c r="J94" s="37" t="n"/>
+      <c r="K94" s="36" t="n"/>
     </row>
     <row r="95" ht="28" customHeight="1">
       <c r="A95" s="36" t="n"/>
@@ -19044,6 +19451,7 @@
       <c r="H95" s="39" t="n"/>
       <c r="I95" s="38" t="n"/>
       <c r="J95" s="37" t="n"/>
+      <c r="K95" s="36" t="n"/>
     </row>
     <row r="96" ht="28" customHeight="1">
       <c r="A96" s="36" t="n"/>
@@ -19056,6 +19464,7 @@
       <c r="H96" s="39" t="n"/>
       <c r="I96" s="38" t="n"/>
       <c r="J96" s="37" t="n"/>
+      <c r="K96" s="36" t="n"/>
     </row>
     <row r="97" ht="28" customHeight="1">
       <c r="A97" s="36" t="n"/>
@@ -19068,6 +19477,7 @@
       <c r="H97" s="39" t="n"/>
       <c r="I97" s="38" t="n"/>
       <c r="J97" s="37" t="n"/>
+      <c r="K97" s="36" t="n"/>
     </row>
     <row r="98" ht="28" customHeight="1">
       <c r="A98" s="36" t="n"/>
@@ -19080,6 +19490,7 @@
       <c r="H98" s="39" t="n"/>
       <c r="I98" s="38" t="n"/>
       <c r="J98" s="37" t="n"/>
+      <c r="K98" s="36" t="n"/>
     </row>
     <row r="99" ht="28" customHeight="1">
       <c r="A99" s="36" t="n"/>
@@ -19092,6 +19503,7 @@
       <c r="H99" s="39" t="n"/>
       <c r="I99" s="38" t="n"/>
       <c r="J99" s="37" t="n"/>
+      <c r="K99" s="36" t="n"/>
     </row>
     <row r="100" ht="28" customHeight="1">
       <c r="A100" s="36" t="n"/>
@@ -19104,6 +19516,7 @@
       <c r="H100" s="39" t="n"/>
       <c r="I100" s="38" t="n"/>
       <c r="J100" s="37" t="n"/>
+      <c r="K100" s="36" t="n"/>
     </row>
     <row r="101" ht="28" customHeight="1">
       <c r="A101" s="36" t="n"/>
@@ -19116,6 +19529,7 @@
       <c r="H101" s="39" t="n"/>
       <c r="I101" s="38" t="n"/>
       <c r="J101" s="37" t="n"/>
+      <c r="K101" s="36" t="n"/>
     </row>
     <row r="102" ht="28" customHeight="1">
       <c r="A102" s="36" t="n"/>
@@ -19128,6 +19542,7 @@
       <c r="H102" s="39" t="n"/>
       <c r="I102" s="38" t="n"/>
       <c r="J102" s="37" t="n"/>
+      <c r="K102" s="36" t="n"/>
     </row>
     <row r="103" ht="28" customHeight="1">
       <c r="A103" s="36" t="n"/>
@@ -19140,6 +19555,7 @@
       <c r="H103" s="39" t="n"/>
       <c r="I103" s="38" t="n"/>
       <c r="J103" s="37" t="n"/>
+      <c r="K103" s="36" t="n"/>
     </row>
     <row r="104" ht="28" customHeight="1">
       <c r="A104" s="36" t="n"/>
@@ -19152,6 +19568,7 @@
       <c r="H104" s="39" t="n"/>
       <c r="I104" s="38" t="n"/>
       <c r="J104" s="37" t="n"/>
+      <c r="K104" s="36" t="n"/>
     </row>
     <row r="105" ht="28" customHeight="1">
       <c r="A105" s="36" t="n"/>
@@ -19164,6 +19581,7 @@
       <c r="H105" s="39" t="n"/>
       <c r="I105" s="38" t="n"/>
       <c r="J105" s="37" t="n"/>
+      <c r="K105" s="36" t="n"/>
     </row>
     <row r="106" ht="28" customHeight="1">
       <c r="A106" s="36" t="n"/>
@@ -19176,6 +19594,7 @@
       <c r="H106" s="39" t="n"/>
       <c r="I106" s="38" t="n"/>
       <c r="J106" s="37" t="n"/>
+      <c r="K106" s="36" t="n"/>
     </row>
     <row r="107" ht="28" customHeight="1">
       <c r="A107" s="36" t="n"/>
@@ -19188,6 +19607,7 @@
       <c r="H107" s="39" t="n"/>
       <c r="I107" s="38" t="n"/>
       <c r="J107" s="37" t="n"/>
+      <c r="K107" s="36" t="n"/>
     </row>
     <row r="108" ht="28" customHeight="1">
       <c r="A108" s="36" t="n"/>
@@ -19200,6 +19620,7 @@
       <c r="H108" s="39" t="n"/>
       <c r="I108" s="38" t="n"/>
       <c r="J108" s="37" t="n"/>
+      <c r="K108" s="36" t="n"/>
     </row>
     <row r="109" ht="28" customHeight="1">
       <c r="A109" s="36" t="n"/>
@@ -19212,6 +19633,7 @@
       <c r="H109" s="39" t="n"/>
       <c r="I109" s="38" t="n"/>
       <c r="J109" s="37" t="n"/>
+      <c r="K109" s="36" t="n"/>
     </row>
     <row r="110" ht="28" customHeight="1">
       <c r="A110" s="36" t="n"/>
@@ -19224,6 +19646,7 @@
       <c r="H110" s="39" t="n"/>
       <c r="I110" s="38" t="n"/>
       <c r="J110" s="37" t="n"/>
+      <c r="K110" s="36" t="n"/>
     </row>
     <row r="111" ht="28" customHeight="1">
       <c r="A111" s="36" t="n"/>
@@ -19236,6 +19659,7 @@
       <c r="H111" s="39" t="n"/>
       <c r="I111" s="38" t="n"/>
       <c r="J111" s="37" t="n"/>
+      <c r="K111" s="36" t="n"/>
     </row>
     <row r="112" ht="28" customHeight="1">
       <c r="A112" s="36" t="n"/>
@@ -19248,6 +19672,7 @@
       <c r="H112" s="39" t="n"/>
       <c r="I112" s="38" t="n"/>
       <c r="J112" s="37" t="n"/>
+      <c r="K112" s="36" t="n"/>
     </row>
     <row r="113" ht="28" customHeight="1">
       <c r="A113" s="36" t="n"/>
@@ -19260,6 +19685,7 @@
       <c r="H113" s="39" t="n"/>
       <c r="I113" s="38" t="n"/>
       <c r="J113" s="37" t="n"/>
+      <c r="K113" s="36" t="n"/>
     </row>
     <row r="114" ht="28" customHeight="1">
       <c r="A114" s="36" t="n"/>
@@ -19272,6 +19698,7 @@
       <c r="H114" s="39" t="n"/>
       <c r="I114" s="38" t="n"/>
       <c r="J114" s="37" t="n"/>
+      <c r="K114" s="36" t="n"/>
     </row>
     <row r="115" ht="28" customHeight="1">
       <c r="A115" s="36" t="n"/>
@@ -19284,6 +19711,7 @@
       <c r="H115" s="39" t="n"/>
       <c r="I115" s="38" t="n"/>
       <c r="J115" s="37" t="n"/>
+      <c r="K115" s="36" t="n"/>
     </row>
     <row r="116" ht="28" customHeight="1">
       <c r="A116" s="36" t="n"/>
@@ -19296,6 +19724,7 @@
       <c r="H116" s="39" t="n"/>
       <c r="I116" s="38" t="n"/>
       <c r="J116" s="37" t="n"/>
+      <c r="K116" s="36" t="n"/>
     </row>
     <row r="117" ht="28" customHeight="1">
       <c r="A117" s="36" t="n"/>
@@ -19308,6 +19737,7 @@
       <c r="H117" s="39" t="n"/>
       <c r="I117" s="38" t="n"/>
       <c r="J117" s="37" t="n"/>
+      <c r="K117" s="36" t="n"/>
     </row>
     <row r="118" ht="28" customHeight="1">
       <c r="A118" s="36" t="n"/>
@@ -19320,6 +19750,7 @@
       <c r="H118" s="39" t="n"/>
       <c r="I118" s="38" t="n"/>
       <c r="J118" s="37" t="n"/>
+      <c r="K118" s="36" t="n"/>
     </row>
     <row r="119" ht="28" customHeight="1">
       <c r="A119" s="36" t="n"/>
@@ -19332,6 +19763,7 @@
       <c r="H119" s="39" t="n"/>
       <c r="I119" s="38" t="n"/>
       <c r="J119" s="37" t="n"/>
+      <c r="K119" s="36" t="n"/>
     </row>
     <row r="120" ht="28" customHeight="1">
       <c r="A120" s="36" t="n"/>
@@ -19344,6 +19776,7 @@
       <c r="H120" s="39" t="n"/>
       <c r="I120" s="38" t="n"/>
       <c r="J120" s="37" t="n"/>
+      <c r="K120" s="36" t="n"/>
     </row>
     <row r="121" ht="28" customHeight="1">
       <c r="A121" s="36" t="n"/>
@@ -19356,6 +19789,7 @@
       <c r="H121" s="39" t="n"/>
       <c r="I121" s="38" t="n"/>
       <c r="J121" s="37" t="n"/>
+      <c r="K121" s="36" t="n"/>
     </row>
     <row r="122" ht="28" customHeight="1">
       <c r="A122" s="36" t="n"/>
@@ -19368,6 +19802,7 @@
       <c r="H122" s="39" t="n"/>
       <c r="I122" s="38" t="n"/>
       <c r="J122" s="37" t="n"/>
+      <c r="K122" s="36" t="n"/>
     </row>
     <row r="123" ht="28" customHeight="1">
       <c r="A123" s="36" t="n"/>
@@ -19380,6 +19815,7 @@
       <c r="H123" s="39" t="n"/>
       <c r="I123" s="38" t="n"/>
       <c r="J123" s="37" t="n"/>
+      <c r="K123" s="36" t="n"/>
     </row>
     <row r="124" ht="28" customHeight="1">
       <c r="A124" s="36" t="n"/>
@@ -19392,6 +19828,7 @@
       <c r="H124" s="39" t="n"/>
       <c r="I124" s="38" t="n"/>
       <c r="J124" s="37" t="n"/>
+      <c r="K124" s="36" t="n"/>
     </row>
     <row r="125" ht="28" customHeight="1">
       <c r="A125" s="36" t="n"/>
@@ -19404,6 +19841,7 @@
       <c r="H125" s="39" t="n"/>
       <c r="I125" s="38" t="n"/>
       <c r="J125" s="37" t="n"/>
+      <c r="K125" s="36" t="n"/>
     </row>
     <row r="126" ht="28" customHeight="1">
       <c r="A126" s="36" t="n"/>
@@ -19416,6 +19854,7 @@
       <c r="H126" s="39" t="n"/>
       <c r="I126" s="38" t="n"/>
       <c r="J126" s="37" t="n"/>
+      <c r="K126" s="36" t="n"/>
     </row>
     <row r="127" ht="28" customHeight="1">
       <c r="A127" s="36" t="n"/>
@@ -19428,6 +19867,7 @@
       <c r="H127" s="39" t="n"/>
       <c r="I127" s="38" t="n"/>
       <c r="J127" s="37" t="n"/>
+      <c r="K127" s="36" t="n"/>
     </row>
     <row r="128" ht="28" customHeight="1">
       <c r="A128" s="36" t="n"/>
@@ -19440,6 +19880,7 @@
       <c r="H128" s="39" t="n"/>
       <c r="I128" s="38" t="n"/>
       <c r="J128" s="37" t="n"/>
+      <c r="K128" s="36" t="n"/>
     </row>
     <row r="129" ht="28" customHeight="1">
       <c r="A129" s="36" t="n"/>
@@ -19452,6 +19893,7 @@
       <c r="H129" s="39" t="n"/>
       <c r="I129" s="38" t="n"/>
       <c r="J129" s="37" t="n"/>
+      <c r="K129" s="36" t="n"/>
     </row>
     <row r="130" ht="28" customHeight="1">
       <c r="A130" s="36" t="n"/>
@@ -19464,6 +19906,7 @@
       <c r="H130" s="39" t="n"/>
       <c r="I130" s="38" t="n"/>
       <c r="J130" s="37" t="n"/>
+      <c r="K130" s="36" t="n"/>
     </row>
     <row r="131" ht="28" customHeight="1">
       <c r="A131" s="36" t="n"/>
@@ -19476,6 +19919,7 @@
       <c r="H131" s="39" t="n"/>
       <c r="I131" s="38" t="n"/>
       <c r="J131" s="37" t="n"/>
+      <c r="K131" s="36" t="n"/>
     </row>
     <row r="132" ht="28" customHeight="1">
       <c r="A132" s="36" t="n"/>
@@ -19488,6 +19932,7 @@
       <c r="H132" s="39" t="n"/>
       <c r="I132" s="38" t="n"/>
       <c r="J132" s="37" t="n"/>
+      <c r="K132" s="36" t="n"/>
     </row>
     <row r="133" ht="28" customHeight="1">
       <c r="A133" s="36" t="n"/>
@@ -19500,6 +19945,7 @@
       <c r="H133" s="39" t="n"/>
       <c r="I133" s="38" t="n"/>
       <c r="J133" s="37" t="n"/>
+      <c r="K133" s="36" t="n"/>
     </row>
     <row r="134" ht="28" customHeight="1">
       <c r="A134" s="36" t="n"/>
@@ -19512,6 +19958,7 @@
       <c r="H134" s="39" t="n"/>
       <c r="I134" s="38" t="n"/>
       <c r="J134" s="37" t="n"/>
+      <c r="K134" s="36" t="n"/>
     </row>
     <row r="135" ht="28" customHeight="1">
       <c r="A135" s="36" t="n"/>
@@ -19524,6 +19971,7 @@
       <c r="H135" s="39" t="n"/>
       <c r="I135" s="38" t="n"/>
       <c r="J135" s="37" t="n"/>
+      <c r="K135" s="36" t="n"/>
     </row>
     <row r="136" ht="28" customHeight="1">
       <c r="A136" s="36" t="n"/>
@@ -19536,6 +19984,7 @@
       <c r="H136" s="39" t="n"/>
       <c r="I136" s="38" t="n"/>
       <c r="J136" s="37" t="n"/>
+      <c r="K136" s="36" t="n"/>
     </row>
     <row r="137" ht="28" customHeight="1">
       <c r="A137" s="36" t="n"/>
@@ -19548,6 +19997,7 @@
       <c r="H137" s="39" t="n"/>
       <c r="I137" s="38" t="n"/>
       <c r="J137" s="37" t="n"/>
+      <c r="K137" s="36" t="n"/>
     </row>
     <row r="138" ht="28" customHeight="1">
       <c r="A138" s="36" t="n"/>
@@ -19560,6 +20010,7 @@
       <c r="H138" s="39" t="n"/>
       <c r="I138" s="38" t="n"/>
       <c r="J138" s="37" t="n"/>
+      <c r="K138" s="36" t="n"/>
     </row>
     <row r="139" ht="28" customHeight="1">
       <c r="A139" s="36" t="n"/>
@@ -19572,6 +20023,7 @@
       <c r="H139" s="39" t="n"/>
       <c r="I139" s="38" t="n"/>
       <c r="J139" s="37" t="n"/>
+      <c r="K139" s="36" t="n"/>
     </row>
     <row r="140" ht="28" customHeight="1">
       <c r="A140" s="36" t="n"/>
@@ -19584,6 +20036,7 @@
       <c r="H140" s="39" t="n"/>
       <c r="I140" s="38" t="n"/>
       <c r="J140" s="37" t="n"/>
+      <c r="K140" s="36" t="n"/>
     </row>
     <row r="141" ht="28" customHeight="1">
       <c r="A141" s="36" t="n"/>
@@ -19596,6 +20049,7 @@
       <c r="H141" s="39" t="n"/>
       <c r="I141" s="38" t="n"/>
       <c r="J141" s="37" t="n"/>
+      <c r="K141" s="36" t="n"/>
     </row>
     <row r="142" ht="28" customHeight="1">
       <c r="A142" s="36" t="n"/>
@@ -19608,6 +20062,7 @@
       <c r="H142" s="39" t="n"/>
       <c r="I142" s="38" t="n"/>
       <c r="J142" s="37" t="n"/>
+      <c r="K142" s="36" t="n"/>
     </row>
     <row r="143" ht="28" customHeight="1">
       <c r="A143" s="36" t="n"/>
@@ -19620,6 +20075,7 @@
       <c r="H143" s="39" t="n"/>
       <c r="I143" s="38" t="n"/>
       <c r="J143" s="37" t="n"/>
+      <c r="K143" s="36" t="n"/>
     </row>
     <row r="144" ht="28" customHeight="1">
       <c r="A144" s="36" t="n"/>
@@ -19632,6 +20088,7 @@
       <c r="H144" s="39" t="n"/>
       <c r="I144" s="38" t="n"/>
       <c r="J144" s="37" t="n"/>
+      <c r="K144" s="36" t="n"/>
     </row>
     <row r="145" ht="28" customHeight="1">
       <c r="A145" s="36" t="n"/>
@@ -19644,6 +20101,7 @@
       <c r="H145" s="39" t="n"/>
       <c r="I145" s="38" t="n"/>
       <c r="J145" s="37" t="n"/>
+      <c r="K145" s="36" t="n"/>
     </row>
     <row r="146" ht="28" customHeight="1">
       <c r="A146" s="36" t="n"/>
@@ -19656,6 +20114,7 @@
       <c r="H146" s="39" t="n"/>
       <c r="I146" s="38" t="n"/>
       <c r="J146" s="37" t="n"/>
+      <c r="K146" s="36" t="n"/>
     </row>
     <row r="147" ht="28" customHeight="1">
       <c r="A147" s="36" t="n"/>
@@ -19668,6 +20127,7 @@
       <c r="H147" s="39" t="n"/>
       <c r="I147" s="38" t="n"/>
       <c r="J147" s="37" t="n"/>
+      <c r="K147" s="36" t="n"/>
     </row>
     <row r="148" ht="28" customHeight="1">
       <c r="A148" s="36" t="n"/>
@@ -19680,6 +20140,7 @@
       <c r="H148" s="39" t="n"/>
       <c r="I148" s="38" t="n"/>
       <c r="J148" s="37" t="n"/>
+      <c r="K148" s="36" t="n"/>
     </row>
     <row r="149" ht="28" customHeight="1">
       <c r="A149" s="36" t="n"/>
@@ -19692,6 +20153,7 @@
       <c r="H149" s="39" t="n"/>
       <c r="I149" s="38" t="n"/>
       <c r="J149" s="37" t="n"/>
+      <c r="K149" s="36" t="n"/>
     </row>
     <row r="150" ht="28" customHeight="1">
       <c r="A150" s="36" t="n"/>
@@ -19704,6 +20166,7 @@
       <c r="H150" s="39" t="n"/>
       <c r="I150" s="38" t="n"/>
       <c r="J150" s="37" t="n"/>
+      <c r="K150" s="36" t="n"/>
     </row>
     <row r="151" ht="28" customHeight="1">
       <c r="A151" s="36" t="n"/>
@@ -19716,6 +20179,7 @@
       <c r="H151" s="39" t="n"/>
       <c r="I151" s="38" t="n"/>
       <c r="J151" s="37" t="n"/>
+      <c r="K151" s="36" t="n"/>
     </row>
     <row r="152" ht="28" customHeight="1">
       <c r="A152" s="36" t="n"/>
@@ -19728,6 +20192,7 @@
       <c r="H152" s="39" t="n"/>
       <c r="I152" s="38" t="n"/>
       <c r="J152" s="37" t="n"/>
+      <c r="K152" s="36" t="n"/>
     </row>
     <row r="153" ht="28" customHeight="1">
       <c r="A153" s="36" t="n"/>
@@ -19740,6 +20205,7 @@
       <c r="H153" s="39" t="n"/>
       <c r="I153" s="38" t="n"/>
       <c r="J153" s="37" t="n"/>
+      <c r="K153" s="36" t="n"/>
     </row>
     <row r="154" ht="28" customHeight="1">
       <c r="A154" s="36" t="n"/>
@@ -19752,6 +20218,7 @@
       <c r="H154" s="39" t="n"/>
       <c r="I154" s="38" t="n"/>
       <c r="J154" s="37" t="n"/>
+      <c r="K154" s="36" t="n"/>
     </row>
     <row r="155" ht="28" customHeight="1">
       <c r="A155" s="36" t="n"/>
@@ -19764,6 +20231,7 @@
       <c r="H155" s="39" t="n"/>
       <c r="I155" s="38" t="n"/>
       <c r="J155" s="37" t="n"/>
+      <c r="K155" s="36" t="n"/>
     </row>
     <row r="156" ht="28" customHeight="1">
       <c r="A156" s="36" t="n"/>
@@ -19776,6 +20244,7 @@
       <c r="H156" s="39" t="n"/>
       <c r="I156" s="38" t="n"/>
       <c r="J156" s="37" t="n"/>
+      <c r="K156" s="36" t="n"/>
     </row>
     <row r="157" ht="28" customHeight="1">
       <c r="A157" s="36" t="n"/>
@@ -19788,6 +20257,7 @@
       <c r="H157" s="39" t="n"/>
       <c r="I157" s="38" t="n"/>
       <c r="J157" s="37" t="n"/>
+      <c r="K157" s="36" t="n"/>
     </row>
     <row r="158" ht="28" customHeight="1">
       <c r="A158" s="36" t="n"/>
@@ -19800,6 +20270,7 @@
       <c r="H158" s="39" t="n"/>
       <c r="I158" s="38" t="n"/>
       <c r="J158" s="37" t="n"/>
+      <c r="K158" s="36" t="n"/>
     </row>
     <row r="159" ht="28" customHeight="1">
       <c r="A159" s="36" t="n"/>
@@ -19812,6 +20283,7 @@
       <c r="H159" s="39" t="n"/>
       <c r="I159" s="38" t="n"/>
       <c r="J159" s="37" t="n"/>
+      <c r="K159" s="36" t="n"/>
     </row>
     <row r="160" ht="28" customHeight="1">
       <c r="A160" s="36" t="n"/>
@@ -19824,6 +20296,7 @@
       <c r="H160" s="39" t="n"/>
       <c r="I160" s="38" t="n"/>
       <c r="J160" s="37" t="n"/>
+      <c r="K160" s="36" t="n"/>
     </row>
     <row r="161" ht="28" customHeight="1">
       <c r="A161" s="36" t="n"/>
@@ -19836,6 +20309,7 @@
       <c r="H161" s="39" t="n"/>
       <c r="I161" s="38" t="n"/>
       <c r="J161" s="37" t="n"/>
+      <c r="K161" s="36" t="n"/>
     </row>
     <row r="162" ht="28" customHeight="1">
       <c r="A162" s="36" t="n"/>
@@ -19848,6 +20322,7 @@
       <c r="H162" s="39" t="n"/>
       <c r="I162" s="38" t="n"/>
       <c r="J162" s="37" t="n"/>
+      <c r="K162" s="36" t="n"/>
     </row>
     <row r="163" ht="28" customHeight="1">
       <c r="A163" s="36" t="n"/>
@@ -19860,6 +20335,7 @@
       <c r="H163" s="39" t="n"/>
       <c r="I163" s="38" t="n"/>
       <c r="J163" s="37" t="n"/>
+      <c r="K163" s="36" t="n"/>
     </row>
     <row r="164" ht="28" customHeight="1">
       <c r="A164" s="36" t="n"/>
@@ -19872,6 +20348,7 @@
       <c r="H164" s="39" t="n"/>
       <c r="I164" s="38" t="n"/>
       <c r="J164" s="37" t="n"/>
+      <c r="K164" s="36" t="n"/>
     </row>
     <row r="165" ht="28" customHeight="1">
       <c r="A165" s="36" t="n"/>
@@ -19884,6 +20361,7 @@
       <c r="H165" s="39" t="n"/>
       <c r="I165" s="38" t="n"/>
       <c r="J165" s="37" t="n"/>
+      <c r="K165" s="36" t="n"/>
     </row>
     <row r="166" ht="28" customHeight="1">
       <c r="A166" s="36" t="n"/>
@@ -19896,6 +20374,7 @@
       <c r="H166" s="39" t="n"/>
       <c r="I166" s="38" t="n"/>
       <c r="J166" s="37" t="n"/>
+      <c r="K166" s="36" t="n"/>
     </row>
     <row r="167" ht="28" customHeight="1">
       <c r="A167" s="36" t="n"/>
@@ -19908,6 +20387,7 @@
       <c r="H167" s="39" t="n"/>
       <c r="I167" s="38" t="n"/>
       <c r="J167" s="37" t="n"/>
+      <c r="K167" s="36" t="n"/>
     </row>
     <row r="168" ht="28" customHeight="1">
       <c r="A168" s="36" t="n"/>
@@ -19920,6 +20400,7 @@
       <c r="H168" s="39" t="n"/>
       <c r="I168" s="38" t="n"/>
       <c r="J168" s="37" t="n"/>
+      <c r="K168" s="36" t="n"/>
     </row>
     <row r="169" ht="28" customHeight="1">
       <c r="A169" s="36" t="n"/>
@@ -19932,6 +20413,7 @@
       <c r="H169" s="39" t="n"/>
       <c r="I169" s="38" t="n"/>
       <c r="J169" s="37" t="n"/>
+      <c r="K169" s="36" t="n"/>
     </row>
     <row r="170" ht="28" customHeight="1">
       <c r="A170" s="36" t="n"/>
@@ -19944,6 +20426,7 @@
       <c r="H170" s="39" t="n"/>
       <c r="I170" s="38" t="n"/>
       <c r="J170" s="37" t="n"/>
+      <c r="K170" s="36" t="n"/>
     </row>
     <row r="171" ht="28" customHeight="1">
       <c r="A171" s="36" t="n"/>
@@ -19956,6 +20439,7 @@
       <c r="H171" s="39" t="n"/>
       <c r="I171" s="38" t="n"/>
       <c r="J171" s="37" t="n"/>
+      <c r="K171" s="36" t="n"/>
     </row>
     <row r="172" ht="28" customHeight="1">
       <c r="A172" s="36" t="n"/>
@@ -19968,6 +20452,7 @@
       <c r="H172" s="39" t="n"/>
       <c r="I172" s="38" t="n"/>
       <c r="J172" s="37" t="n"/>
+      <c r="K172" s="36" t="n"/>
     </row>
     <row r="173" ht="28" customHeight="1">
       <c r="A173" s="36" t="n"/>
@@ -19980,6 +20465,7 @@
       <c r="H173" s="39" t="n"/>
       <c r="I173" s="38" t="n"/>
       <c r="J173" s="37" t="n"/>
+      <c r="K173" s="36" t="n"/>
     </row>
     <row r="174" ht="28" customHeight="1">
       <c r="A174" s="36" t="n"/>
@@ -19992,6 +20478,7 @@
       <c r="H174" s="39" t="n"/>
       <c r="I174" s="38" t="n"/>
       <c r="J174" s="37" t="n"/>
+      <c r="K174" s="36" t="n"/>
     </row>
     <row r="175" ht="28" customHeight="1">
       <c r="A175" s="36" t="n"/>
@@ -20004,6 +20491,7 @@
       <c r="H175" s="39" t="n"/>
       <c r="I175" s="38" t="n"/>
       <c r="J175" s="37" t="n"/>
+      <c r="K175" s="36" t="n"/>
     </row>
     <row r="176" ht="28" customHeight="1">
       <c r="A176" s="36" t="n"/>
@@ -20016,6 +20504,7 @@
       <c r="H176" s="39" t="n"/>
       <c r="I176" s="38" t="n"/>
       <c r="J176" s="37" t="n"/>
+      <c r="K176" s="36" t="n"/>
     </row>
     <row r="177" ht="28" customHeight="1">
       <c r="A177" s="36" t="n"/>
@@ -20028,6 +20517,7 @@
       <c r="H177" s="39" t="n"/>
       <c r="I177" s="38" t="n"/>
       <c r="J177" s="37" t="n"/>
+      <c r="K177" s="36" t="n"/>
     </row>
     <row r="178" ht="28" customHeight="1">
       <c r="A178" s="36" t="n"/>
@@ -20040,6 +20530,7 @@
       <c r="H178" s="39" t="n"/>
       <c r="I178" s="38" t="n"/>
       <c r="J178" s="37" t="n"/>
+      <c r="K178" s="36" t="n"/>
     </row>
     <row r="179" ht="28" customHeight="1">
       <c r="A179" s="36" t="n"/>
@@ -20052,6 +20543,7 @@
       <c r="H179" s="39" t="n"/>
       <c r="I179" s="38" t="n"/>
       <c r="J179" s="37" t="n"/>
+      <c r="K179" s="36" t="n"/>
     </row>
     <row r="180" ht="28" customHeight="1">
       <c r="A180" s="36" t="n"/>
@@ -20064,6 +20556,7 @@
       <c r="H180" s="39" t="n"/>
       <c r="I180" s="38" t="n"/>
       <c r="J180" s="37" t="n"/>
+      <c r="K180" s="36" t="n"/>
     </row>
     <row r="181" ht="28" customHeight="1">
       <c r="A181" s="36" t="n"/>
@@ -20076,6 +20569,7 @@
       <c r="H181" s="39" t="n"/>
       <c r="I181" s="38" t="n"/>
       <c r="J181" s="37" t="n"/>
+      <c r="K181" s="36" t="n"/>
     </row>
     <row r="182" ht="28" customHeight="1">
       <c r="A182" s="36" t="n"/>
@@ -20088,6 +20582,7 @@
       <c r="H182" s="39" t="n"/>
       <c r="I182" s="38" t="n"/>
       <c r="J182" s="37" t="n"/>
+      <c r="K182" s="36" t="n"/>
     </row>
     <row r="183" ht="28" customHeight="1">
       <c r="A183" s="36" t="n"/>
@@ -20100,6 +20595,7 @@
       <c r="H183" s="39" t="n"/>
       <c r="I183" s="38" t="n"/>
       <c r="J183" s="37" t="n"/>
+      <c r="K183" s="36" t="n"/>
     </row>
     <row r="184" ht="28" customHeight="1">
       <c r="A184" s="36" t="n"/>
@@ -20112,6 +20608,7 @@
       <c r="H184" s="39" t="n"/>
       <c r="I184" s="38" t="n"/>
       <c r="J184" s="37" t="n"/>
+      <c r="K184" s="36" t="n"/>
     </row>
     <row r="185" ht="28" customHeight="1">
       <c r="A185" s="36" t="n"/>
@@ -20124,6 +20621,7 @@
       <c r="H185" s="39" t="n"/>
       <c r="I185" s="38" t="n"/>
       <c r="J185" s="37" t="n"/>
+      <c r="K185" s="36" t="n"/>
     </row>
     <row r="186" ht="28" customHeight="1">
       <c r="A186" s="36" t="n"/>
@@ -20136,6 +20634,7 @@
       <c r="H186" s="39" t="n"/>
       <c r="I186" s="38" t="n"/>
       <c r="J186" s="37" t="n"/>
+      <c r="K186" s="36" t="n"/>
     </row>
     <row r="187" ht="28" customHeight="1">
       <c r="A187" s="36" t="n"/>
@@ -20148,6 +20647,7 @@
       <c r="H187" s="39" t="n"/>
       <c r="I187" s="38" t="n"/>
       <c r="J187" s="37" t="n"/>
+      <c r="K187" s="36" t="n"/>
     </row>
     <row r="188" ht="28" customHeight="1">
       <c r="A188" s="36" t="n"/>
@@ -20160,6 +20660,7 @@
       <c r="H188" s="39" t="n"/>
       <c r="I188" s="38" t="n"/>
       <c r="J188" s="37" t="n"/>
+      <c r="K188" s="36" t="n"/>
     </row>
     <row r="189" ht="28" customHeight="1">
       <c r="A189" s="36" t="n"/>
@@ -20172,6 +20673,7 @@
       <c r="H189" s="39" t="n"/>
       <c r="I189" s="38" t="n"/>
       <c r="J189" s="37" t="n"/>
+      <c r="K189" s="36" t="n"/>
     </row>
     <row r="190" ht="28" customHeight="1">
       <c r="A190" s="36" t="n"/>
@@ -20184,6 +20686,7 @@
       <c r="H190" s="39" t="n"/>
       <c r="I190" s="38" t="n"/>
       <c r="J190" s="37" t="n"/>
+      <c r="K190" s="36" t="n"/>
     </row>
     <row r="191" ht="28" customHeight="1">
       <c r="A191" s="36" t="n"/>
@@ -20196,6 +20699,7 @@
       <c r="H191" s="39" t="n"/>
       <c r="I191" s="38" t="n"/>
       <c r="J191" s="37" t="n"/>
+      <c r="K191" s="36" t="n"/>
     </row>
     <row r="192" ht="28" customHeight="1">
       <c r="A192" s="36" t="n"/>
@@ -20208,6 +20712,7 @@
       <c r="H192" s="39" t="n"/>
       <c r="I192" s="38" t="n"/>
       <c r="J192" s="37" t="n"/>
+      <c r="K192" s="36" t="n"/>
     </row>
     <row r="193" ht="28" customHeight="1">
       <c r="A193" s="36" t="n"/>
@@ -20220,6 +20725,7 @@
       <c r="H193" s="39" t="n"/>
       <c r="I193" s="38" t="n"/>
       <c r="J193" s="37" t="n"/>
+      <c r="K193" s="36" t="n"/>
     </row>
     <row r="194" ht="28" customHeight="1">
       <c r="A194" s="36" t="n"/>
@@ -20232,6 +20738,7 @@
       <c r="H194" s="39" t="n"/>
       <c r="I194" s="38" t="n"/>
       <c r="J194" s="37" t="n"/>
+      <c r="K194" s="36" t="n"/>
     </row>
     <row r="195" ht="28" customHeight="1">
       <c r="A195" s="36" t="n"/>
@@ -20244,6 +20751,7 @@
       <c r="H195" s="39" t="n"/>
       <c r="I195" s="38" t="n"/>
       <c r="J195" s="37" t="n"/>
+      <c r="K195" s="36" t="n"/>
     </row>
     <row r="196" ht="28" customHeight="1">
       <c r="A196" s="36" t="n"/>
@@ -20256,6 +20764,7 @@
       <c r="H196" s="39" t="n"/>
       <c r="I196" s="38" t="n"/>
       <c r="J196" s="37" t="n"/>
+      <c r="K196" s="36" t="n"/>
     </row>
     <row r="197" ht="28" customHeight="1">
       <c r="A197" s="36" t="n"/>
@@ -20268,6 +20777,7 @@
       <c r="H197" s="39" t="n"/>
       <c r="I197" s="38" t="n"/>
       <c r="J197" s="37" t="n"/>
+      <c r="K197" s="36" t="n"/>
     </row>
     <row r="198" ht="28" customHeight="1">
       <c r="A198" s="36" t="n"/>
@@ -20280,6 +20790,7 @@
       <c r="H198" s="39" t="n"/>
       <c r="I198" s="38" t="n"/>
       <c r="J198" s="37" t="n"/>
+      <c r="K198" s="36" t="n"/>
     </row>
     <row r="199" ht="28" customHeight="1">
       <c r="A199" s="36" t="n"/>
@@ -20292,6 +20803,7 @@
       <c r="H199" s="39" t="n"/>
       <c r="I199" s="38" t="n"/>
       <c r="J199" s="37" t="n"/>
+      <c r="K199" s="36" t="n"/>
     </row>
     <row r="200" ht="28" customHeight="1">
       <c r="A200" s="36" t="n"/>
@@ -20304,6 +20816,7 @@
       <c r="H200" s="39" t="n"/>
       <c r="I200" s="38" t="n"/>
       <c r="J200" s="37" t="n"/>
+      <c r="K200" s="36" t="n"/>
     </row>
     <row r="201" ht="28" customHeight="1">
       <c r="A201" s="36" t="n"/>
@@ -20316,6 +20829,7 @@
       <c r="H201" s="39" t="n"/>
       <c r="I201" s="38" t="n"/>
       <c r="J201" s="37" t="n"/>
+      <c r="K201" s="36" t="n"/>
     </row>
     <row r="202" ht="28" customHeight="1">
       <c r="A202" s="36" t="n"/>
@@ -20328,6 +20842,7 @@
       <c r="H202" s="39" t="n"/>
       <c r="I202" s="38" t="n"/>
       <c r="J202" s="37" t="n"/>
+      <c r="K202" s="36" t="n"/>
     </row>
     <row r="203" ht="28" customHeight="1">
       <c r="A203" s="36" t="n"/>
@@ -20340,6 +20855,7 @@
       <c r="H203" s="39" t="n"/>
       <c r="I203" s="38" t="n"/>
       <c r="J203" s="37" t="n"/>
+      <c r="K203" s="36" t="n"/>
     </row>
     <row r="204" ht="28" customHeight="1">
       <c r="A204" s="36" t="n"/>
@@ -20352,6 +20868,7 @@
       <c r="H204" s="39" t="n"/>
       <c r="I204" s="38" t="n"/>
       <c r="J204" s="37" t="n"/>
+      <c r="K204" s="36" t="n"/>
     </row>
     <row r="205" ht="28" customHeight="1">
       <c r="A205" s="36" t="n"/>
@@ -20364,6 +20881,7 @@
       <c r="H205" s="39" t="n"/>
       <c r="I205" s="38" t="n"/>
       <c r="J205" s="37" t="n"/>
+      <c r="K205" s="36" t="n"/>
     </row>
     <row r="206" ht="28" customHeight="1">
       <c r="A206" s="36" t="n"/>
@@ -20376,6 +20894,7 @@
       <c r="H206" s="39" t="n"/>
       <c r="I206" s="38" t="n"/>
       <c r="J206" s="37" t="n"/>
+      <c r="K206" s="36" t="n"/>
     </row>
     <row r="207" ht="28" customHeight="1">
       <c r="A207" s="36" t="n"/>
@@ -20388,6 +20907,7 @@
       <c r="H207" s="39" t="n"/>
       <c r="I207" s="38" t="n"/>
       <c r="J207" s="37" t="n"/>
+      <c r="K207" s="36" t="n"/>
     </row>
     <row r="208" ht="28" customHeight="1">
       <c r="A208" s="36" t="n"/>
@@ -20400,6 +20920,7 @@
       <c r="H208" s="39" t="n"/>
       <c r="I208" s="38" t="n"/>
       <c r="J208" s="37" t="n"/>
+      <c r="K208" s="36" t="n"/>
     </row>
     <row r="209" ht="28" customHeight="1">
       <c r="A209" s="36" t="n"/>
@@ -20412,6 +20933,7 @@
       <c r="H209" s="39" t="n"/>
       <c r="I209" s="38" t="n"/>
       <c r="J209" s="37" t="n"/>
+      <c r="K209" s="36" t="n"/>
     </row>
     <row r="210" ht="28" customHeight="1">
       <c r="A210" s="36" t="n"/>
@@ -20424,6 +20946,7 @@
       <c r="H210" s="39" t="n"/>
       <c r="I210" s="38" t="n"/>
       <c r="J210" s="37" t="n"/>
+      <c r="K210" s="36" t="n"/>
     </row>
     <row r="211" ht="28" customHeight="1">
       <c r="A211" s="36" t="n"/>
@@ -20436,6 +20959,7 @@
       <c r="H211" s="39" t="n"/>
       <c r="I211" s="38" t="n"/>
       <c r="J211" s="37" t="n"/>
+      <c r="K211" s="36" t="n"/>
     </row>
     <row r="212" ht="28" customHeight="1">
       <c r="A212" s="36" t="n"/>
@@ -20448,6 +20972,7 @@
       <c r="H212" s="39" t="n"/>
       <c r="I212" s="38" t="n"/>
       <c r="J212" s="37" t="n"/>
+      <c r="K212" s="36" t="n"/>
     </row>
     <row r="213" ht="28" customHeight="1">
       <c r="A213" s="36" t="n"/>
@@ -20460,6 +20985,7 @@
       <c r="H213" s="39" t="n"/>
       <c r="I213" s="38" t="n"/>
       <c r="J213" s="37" t="n"/>
+      <c r="K213" s="36" t="n"/>
     </row>
     <row r="214" ht="28" customHeight="1">
       <c r="A214" s="36" t="n"/>
@@ -20472,6 +20998,7 @@
       <c r="H214" s="39" t="n"/>
       <c r="I214" s="38" t="n"/>
       <c r="J214" s="37" t="n"/>
+      <c r="K214" s="36" t="n"/>
     </row>
     <row r="215" ht="28" customHeight="1">
       <c r="A215" s="36" t="n"/>
@@ -20484,6 +21011,7 @@
       <c r="H215" s="39" t="n"/>
       <c r="I215" s="38" t="n"/>
       <c r="J215" s="37" t="n"/>
+      <c r="K215" s="36" t="n"/>
     </row>
     <row r="216" ht="28" customHeight="1">
       <c r="A216" s="36" t="n"/>
@@ -20496,6 +21024,7 @@
       <c r="H216" s="39" t="n"/>
       <c r="I216" s="38" t="n"/>
       <c r="J216" s="37" t="n"/>
+      <c r="K216" s="36" t="n"/>
     </row>
     <row r="217" ht="28" customHeight="1">
       <c r="A217" s="36" t="n"/>
@@ -20508,6 +21037,7 @@
       <c r="H217" s="39" t="n"/>
       <c r="I217" s="38" t="n"/>
       <c r="J217" s="37" t="n"/>
+      <c r="K217" s="36" t="n"/>
     </row>
     <row r="218" ht="28" customHeight="1">
       <c r="A218" s="36" t="n"/>
@@ -20520,6 +21050,7 @@
       <c r="H218" s="39" t="n"/>
       <c r="I218" s="38" t="n"/>
       <c r="J218" s="37" t="n"/>
+      <c r="K218" s="36" t="n"/>
     </row>
     <row r="219" ht="28" customHeight="1">
       <c r="A219" s="36" t="n"/>
@@ -20532,6 +21063,7 @@
       <c r="H219" s="39" t="n"/>
       <c r="I219" s="38" t="n"/>
       <c r="J219" s="37" t="n"/>
+      <c r="K219" s="36" t="n"/>
     </row>
     <row r="220" ht="28" customHeight="1">
       <c r="A220" s="36" t="n"/>
@@ -20544,6 +21076,7 @@
       <c r="H220" s="39" t="n"/>
       <c r="I220" s="38" t="n"/>
       <c r="J220" s="37" t="n"/>
+      <c r="K220" s="36" t="n"/>
     </row>
     <row r="221" ht="28" customHeight="1">
       <c r="A221" s="36" t="n"/>
@@ -20556,6 +21089,7 @@
       <c r="H221" s="39" t="n"/>
       <c r="I221" s="38" t="n"/>
       <c r="J221" s="37" t="n"/>
+      <c r="K221" s="36" t="n"/>
     </row>
     <row r="222" ht="28" customHeight="1">
       <c r="A222" s="36" t="n"/>
@@ -20568,6 +21102,7 @@
       <c r="H222" s="39" t="n"/>
       <c r="I222" s="38" t="n"/>
       <c r="J222" s="37" t="n"/>
+      <c r="K222" s="36" t="n"/>
     </row>
     <row r="223" ht="28" customHeight="1">
       <c r="A223" s="36" t="n"/>
@@ -20580,6 +21115,7 @@
       <c r="H223" s="39" t="n"/>
       <c r="I223" s="38" t="n"/>
       <c r="J223" s="37" t="n"/>
+      <c r="K223" s="36" t="n"/>
     </row>
     <row r="224" ht="28" customHeight="1">
       <c r="A224" s="36" t="n"/>
@@ -20592,6 +21128,7 @@
       <c r="H224" s="39" t="n"/>
       <c r="I224" s="38" t="n"/>
       <c r="J224" s="37" t="n"/>
+      <c r="K224" s="36" t="n"/>
     </row>
     <row r="225" ht="28" customHeight="1">
       <c r="A225" s="36" t="n"/>
@@ -20604,6 +21141,7 @@
       <c r="H225" s="39" t="n"/>
       <c r="I225" s="38" t="n"/>
       <c r="J225" s="37" t="n"/>
+      <c r="K225" s="36" t="n"/>
     </row>
     <row r="226" ht="28" customHeight="1">
       <c r="A226" s="36" t="n"/>
@@ -20616,6 +21154,7 @@
       <c r="H226" s="39" t="n"/>
       <c r="I226" s="38" t="n"/>
       <c r="J226" s="37" t="n"/>
+      <c r="K226" s="36" t="n"/>
     </row>
     <row r="227" ht="28" customHeight="1">
       <c r="A227" s="36" t="n"/>
@@ -20628,6 +21167,7 @@
       <c r="H227" s="39" t="n"/>
       <c r="I227" s="38" t="n"/>
       <c r="J227" s="37" t="n"/>
+      <c r="K227" s="36" t="n"/>
     </row>
     <row r="228" ht="28" customHeight="1">
       <c r="A228" s="36" t="n"/>
@@ -20640,6 +21180,7 @@
       <c r="H228" s="39" t="n"/>
       <c r="I228" s="38" t="n"/>
       <c r="J228" s="37" t="n"/>
+      <c r="K228" s="36" t="n"/>
     </row>
     <row r="229" ht="28" customHeight="1">
       <c r="A229" s="36" t="n"/>
@@ -20652,6 +21193,7 @@
       <c r="H229" s="39" t="n"/>
       <c r="I229" s="38" t="n"/>
       <c r="J229" s="37" t="n"/>
+      <c r="K229" s="36" t="n"/>
     </row>
     <row r="230" ht="28" customHeight="1">
       <c r="A230" s="36" t="n"/>
@@ -20664,6 +21206,7 @@
       <c r="H230" s="39" t="n"/>
       <c r="I230" s="38" t="n"/>
       <c r="J230" s="37" t="n"/>
+      <c r="K230" s="36" t="n"/>
     </row>
     <row r="231" ht="28" customHeight="1">
       <c r="A231" s="36" t="n"/>
@@ -20676,6 +21219,7 @@
       <c r="H231" s="39" t="n"/>
       <c r="I231" s="38" t="n"/>
       <c r="J231" s="37" t="n"/>
+      <c r="K231" s="36" t="n"/>
     </row>
     <row r="232" ht="28" customHeight="1">
       <c r="A232" s="36" t="n"/>
@@ -20688,6 +21232,7 @@
       <c r="H232" s="39" t="n"/>
       <c r="I232" s="38" t="n"/>
       <c r="J232" s="37" t="n"/>
+      <c r="K232" s="36" t="n"/>
     </row>
     <row r="233" ht="28" customHeight="1">
       <c r="A233" s="36" t="n"/>
@@ -20700,6 +21245,7 @@
       <c r="H233" s="39" t="n"/>
       <c r="I233" s="38" t="n"/>
       <c r="J233" s="37" t="n"/>
+      <c r="K233" s="36" t="n"/>
     </row>
     <row r="234" ht="28" customHeight="1">
       <c r="A234" s="36" t="n"/>
@@ -20712,6 +21258,7 @@
       <c r="H234" s="39" t="n"/>
       <c r="I234" s="38" t="n"/>
       <c r="J234" s="37" t="n"/>
+      <c r="K234" s="36" t="n"/>
     </row>
     <row r="235" ht="28" customHeight="1">
       <c r="A235" s="36" t="n"/>
@@ -20724,6 +21271,7 @@
       <c r="H235" s="39" t="n"/>
       <c r="I235" s="38" t="n"/>
       <c r="J235" s="37" t="n"/>
+      <c r="K235" s="36" t="n"/>
     </row>
     <row r="236" ht="28" customHeight="1">
       <c r="A236" s="36" t="n"/>
@@ -20736,6 +21284,7 @@
       <c r="H236" s="39" t="n"/>
       <c r="I236" s="38" t="n"/>
       <c r="J236" s="37" t="n"/>
+      <c r="K236" s="36" t="n"/>
     </row>
     <row r="237" ht="28" customHeight="1">
       <c r="A237" s="36" t="n"/>
@@ -20748,6 +21297,7 @@
       <c r="H237" s="39" t="n"/>
       <c r="I237" s="38" t="n"/>
       <c r="J237" s="37" t="n"/>
+      <c r="K237" s="36" t="n"/>
     </row>
     <row r="238" ht="28" customHeight="1">
       <c r="A238" s="36" t="n"/>
@@ -20760,6 +21310,7 @@
       <c r="H238" s="39" t="n"/>
       <c r="I238" s="38" t="n"/>
       <c r="J238" s="37" t="n"/>
+      <c r="K238" s="36" t="n"/>
     </row>
     <row r="239" ht="28" customHeight="1">
       <c r="A239" s="36" t="n"/>
@@ -20772,6 +21323,7 @@
       <c r="H239" s="39" t="n"/>
       <c r="I239" s="38" t="n"/>
       <c r="J239" s="37" t="n"/>
+      <c r="K239" s="36" t="n"/>
     </row>
     <row r="240" ht="28" customHeight="1">
       <c r="A240" s="36" t="n"/>
@@ -20784,6 +21336,7 @@
       <c r="H240" s="39" t="n"/>
       <c r="I240" s="38" t="n"/>
       <c r="J240" s="37" t="n"/>
+      <c r="K240" s="36" t="n"/>
     </row>
     <row r="241" ht="28" customHeight="1">
       <c r="A241" s="36" t="n"/>
@@ -20796,6 +21349,7 @@
       <c r="H241" s="39" t="n"/>
       <c r="I241" s="38" t="n"/>
       <c r="J241" s="37" t="n"/>
+      <c r="K241" s="36" t="n"/>
     </row>
     <row r="242" ht="28" customHeight="1">
       <c r="A242" s="36" t="n"/>
@@ -20808,6 +21362,7 @@
       <c r="H242" s="39" t="n"/>
       <c r="I242" s="38" t="n"/>
       <c r="J242" s="37" t="n"/>
+      <c r="K242" s="36" t="n"/>
     </row>
     <row r="243" ht="28" customHeight="1">
       <c r="A243" s="36" t="n"/>
@@ -20820,6 +21375,7 @@
       <c r="H243" s="39" t="n"/>
       <c r="I243" s="38" t="n"/>
       <c r="J243" s="37" t="n"/>
+      <c r="K243" s="36" t="n"/>
     </row>
     <row r="244" ht="28" customHeight="1">
       <c r="A244" s="36" t="n"/>
@@ -20832,6 +21388,7 @@
       <c r="H244" s="39" t="n"/>
       <c r="I244" s="38" t="n"/>
       <c r="J244" s="37" t="n"/>
+      <c r="K244" s="36" t="n"/>
     </row>
     <row r="245" ht="28" customHeight="1">
       <c r="A245" s="36" t="n"/>
@@ -20844,6 +21401,7 @@
       <c r="H245" s="39" t="n"/>
       <c r="I245" s="38" t="n"/>
       <c r="J245" s="37" t="n"/>
+      <c r="K245" s="36" t="n"/>
     </row>
     <row r="246" ht="28" customHeight="1">
       <c r="A246" s="36" t="n"/>
@@ -20856,6 +21414,7 @@
       <c r="H246" s="39" t="n"/>
       <c r="I246" s="38" t="n"/>
       <c r="J246" s="37" t="n"/>
+      <c r="K246" s="36" t="n"/>
     </row>
     <row r="247" ht="28" customHeight="1">
       <c r="A247" s="36" t="n"/>
@@ -20868,6 +21427,7 @@
       <c r="H247" s="39" t="n"/>
       <c r="I247" s="38" t="n"/>
       <c r="J247" s="37" t="n"/>
+      <c r="K247" s="36" t="n"/>
     </row>
     <row r="248" ht="28" customHeight="1">
       <c r="A248" s="36" t="n"/>
@@ -20880,6 +21440,7 @@
       <c r="H248" s="39" t="n"/>
       <c r="I248" s="38" t="n"/>
       <c r="J248" s="37" t="n"/>
+      <c r="K248" s="36" t="n"/>
     </row>
     <row r="249" ht="28" customHeight="1">
       <c r="A249" s="36" t="n"/>
@@ -20892,6 +21453,7 @@
       <c r="H249" s="39" t="n"/>
       <c r="I249" s="38" t="n"/>
       <c r="J249" s="37" t="n"/>
+      <c r="K249" s="36" t="n"/>
     </row>
     <row r="250" ht="28" customHeight="1">
       <c r="A250" s="36" t="n"/>
@@ -20904,6 +21466,7 @@
       <c r="H250" s="39" t="n"/>
       <c r="I250" s="38" t="n"/>
       <c r="J250" s="37" t="n"/>
+      <c r="K250" s="36" t="n"/>
     </row>
     <row r="251" ht="28" customHeight="1">
       <c r="A251" s="36" t="n"/>
@@ -20916,6 +21479,7 @@
       <c r="H251" s="39" t="n"/>
       <c r="I251" s="38" t="n"/>
       <c r="J251" s="37" t="n"/>
+      <c r="K251" s="36" t="n"/>
     </row>
     <row r="252" ht="28" customHeight="1">
       <c r="A252" s="36" t="n"/>
@@ -20928,6 +21492,7 @@
       <c r="H252" s="39" t="n"/>
       <c r="I252" s="38" t="n"/>
       <c r="J252" s="37" t="n"/>
+      <c r="K252" s="36" t="n"/>
     </row>
     <row r="253" ht="28" customHeight="1">
       <c r="A253" s="36" t="n"/>
@@ -20940,6 +21505,7 @@
       <c r="H253" s="39" t="n"/>
       <c r="I253" s="38" t="n"/>
       <c r="J253" s="37" t="n"/>
+      <c r="K253" s="36" t="n"/>
     </row>
     <row r="254" ht="28" customHeight="1">
       <c r="A254" s="36" t="n"/>
@@ -20952,6 +21518,7 @@
       <c r="H254" s="39" t="n"/>
       <c r="I254" s="38" t="n"/>
       <c r="J254" s="37" t="n"/>
+      <c r="K254" s="36" t="n"/>
     </row>
     <row r="255" ht="28" customHeight="1">
       <c r="A255" s="36" t="n"/>
@@ -20964,6 +21531,7 @@
       <c r="H255" s="39" t="n"/>
       <c r="I255" s="38" t="n"/>
       <c r="J255" s="37" t="n"/>
+      <c r="K255" s="36" t="n"/>
     </row>
     <row r="256" ht="28" customHeight="1">
       <c r="A256" s="36" t="n"/>
@@ -20976,6 +21544,7 @@
       <c r="H256" s="39" t="n"/>
       <c r="I256" s="38" t="n"/>
       <c r="J256" s="37" t="n"/>
+      <c r="K256" s="36" t="n"/>
     </row>
     <row r="257" ht="28" customHeight="1">
       <c r="A257" s="36" t="n"/>
@@ -20988,6 +21557,7 @@
       <c r="H257" s="39" t="n"/>
       <c r="I257" s="38" t="n"/>
       <c r="J257" s="37" t="n"/>
+      <c r="K257" s="36" t="n"/>
     </row>
     <row r="258" ht="28" customHeight="1">
       <c r="A258" s="36" t="n"/>
@@ -21000,6 +21570,7 @@
       <c r="H258" s="39" t="n"/>
       <c r="I258" s="38" t="n"/>
       <c r="J258" s="37" t="n"/>
+      <c r="K258" s="36" t="n"/>
     </row>
     <row r="259" ht="28" customHeight="1">
       <c r="A259" s="36" t="n"/>
@@ -21012,6 +21583,7 @@
       <c r="H259" s="39" t="n"/>
       <c r="I259" s="38" t="n"/>
       <c r="J259" s="37" t="n"/>
+      <c r="K259" s="36" t="n"/>
     </row>
     <row r="260" ht="28" customHeight="1">
       <c r="A260" s="36" t="n"/>
@@ -21024,6 +21596,7 @@
       <c r="H260" s="39" t="n"/>
       <c r="I260" s="38" t="n"/>
       <c r="J260" s="37" t="n"/>
+      <c r="K260" s="36" t="n"/>
     </row>
     <row r="261" ht="28" customHeight="1">
       <c r="A261" s="36" t="n"/>
@@ -21036,6 +21609,7 @@
       <c r="H261" s="39" t="n"/>
       <c r="I261" s="38" t="n"/>
       <c r="J261" s="37" t="n"/>
+      <c r="K261" s="36" t="n"/>
     </row>
     <row r="262" ht="28" customHeight="1">
       <c r="A262" s="36" t="n"/>
@@ -21048,6 +21622,7 @@
       <c r="H262" s="39" t="n"/>
       <c r="I262" s="38" t="n"/>
       <c r="J262" s="37" t="n"/>
+      <c r="K262" s="36" t="n"/>
     </row>
     <row r="263" ht="28" customHeight="1">
       <c r="A263" s="36" t="n"/>
@@ -21060,6 +21635,7 @@
       <c r="H263" s="39" t="n"/>
       <c r="I263" s="38" t="n"/>
       <c r="J263" s="37" t="n"/>
+      <c r="K263" s="36" t="n"/>
     </row>
     <row r="264" ht="28" customHeight="1">
       <c r="A264" s="36" t="n"/>
@@ -21072,6 +21648,7 @@
       <c r="H264" s="39" t="n"/>
       <c r="I264" s="38" t="n"/>
       <c r="J264" s="37" t="n"/>
+      <c r="K264" s="36" t="n"/>
     </row>
     <row r="265" ht="28" customHeight="1">
       <c r="A265" s="36" t="n"/>
@@ -21084,6 +21661,7 @@
       <c r="H265" s="39" t="n"/>
       <c r="I265" s="38" t="n"/>
       <c r="J265" s="37" t="n"/>
+      <c r="K265" s="36" t="n"/>
     </row>
     <row r="266" ht="28" customHeight="1">
       <c r="A266" s="36" t="n"/>
@@ -21096,6 +21674,7 @@
       <c r="H266" s="39" t="n"/>
       <c r="I266" s="38" t="n"/>
       <c r="J266" s="37" t="n"/>
+      <c r="K266" s="36" t="n"/>
     </row>
     <row r="267" ht="28" customHeight="1">
       <c r="A267" s="36" t="n"/>
@@ -21108,6 +21687,7 @@
       <c r="H267" s="39" t="n"/>
       <c r="I267" s="38" t="n"/>
       <c r="J267" s="37" t="n"/>
+      <c r="K267" s="36" t="n"/>
     </row>
     <row r="268" ht="28" customHeight="1">
       <c r="A268" s="36" t="n"/>
@@ -21120,6 +21700,7 @@
       <c r="H268" s="39" t="n"/>
       <c r="I268" s="38" t="n"/>
       <c r="J268" s="37" t="n"/>
+      <c r="K268" s="36" t="n"/>
     </row>
     <row r="269" ht="28" customHeight="1">
       <c r="A269" s="36" t="n"/>
@@ -21132,6 +21713,7 @@
       <c r="H269" s="39" t="n"/>
       <c r="I269" s="38" t="n"/>
       <c r="J269" s="37" t="n"/>
+      <c r="K269" s="36" t="n"/>
     </row>
     <row r="270" ht="28" customHeight="1">
       <c r="A270" s="36" t="n"/>
@@ -21144,6 +21726,7 @@
       <c r="H270" s="39" t="n"/>
       <c r="I270" s="38" t="n"/>
       <c r="J270" s="37" t="n"/>
+      <c r="K270" s="36" t="n"/>
     </row>
     <row r="271" ht="28" customHeight="1">
       <c r="A271" s="36" t="n"/>
@@ -21156,6 +21739,7 @@
       <c r="H271" s="39" t="n"/>
       <c r="I271" s="38" t="n"/>
       <c r="J271" s="37" t="n"/>
+      <c r="K271" s="36" t="n"/>
     </row>
     <row r="272" ht="28" customHeight="1">
       <c r="A272" s="36" t="n"/>
@@ -21168,6 +21752,7 @@
       <c r="H272" s="39" t="n"/>
       <c r="I272" s="38" t="n"/>
       <c r="J272" s="37" t="n"/>
+      <c r="K272" s="36" t="n"/>
     </row>
     <row r="273" ht="28" customHeight="1">
       <c r="A273" s="36" t="n"/>
@@ -21180,6 +21765,7 @@
       <c r="H273" s="39" t="n"/>
       <c r="I273" s="38" t="n"/>
       <c r="J273" s="37" t="n"/>
+      <c r="K273" s="36" t="n"/>
     </row>
     <row r="274" ht="28" customHeight="1">
       <c r="A274" s="36" t="n"/>
@@ -21192,6 +21778,7 @@
       <c r="H274" s="39" t="n"/>
       <c r="I274" s="38" t="n"/>
       <c r="J274" s="37" t="n"/>
+      <c r="K274" s="36" t="n"/>
     </row>
     <row r="275" ht="28" customHeight="1">
       <c r="A275" s="36" t="n"/>
@@ -21204,6 +21791,7 @@
       <c r="H275" s="39" t="n"/>
       <c r="I275" s="38" t="n"/>
       <c r="J275" s="37" t="n"/>
+      <c r="K275" s="36" t="n"/>
     </row>
     <row r="276" ht="28" customHeight="1">
       <c r="A276" s="36" t="n"/>
@@ -21216,6 +21804,7 @@
       <c r="H276" s="39" t="n"/>
       <c r="I276" s="38" t="n"/>
       <c r="J276" s="37" t="n"/>
+      <c r="K276" s="36" t="n"/>
     </row>
     <row r="277" ht="28" customHeight="1">
       <c r="A277" s="36" t="n"/>
@@ -21228,6 +21817,7 @@
       <c r="H277" s="39" t="n"/>
       <c r="I277" s="38" t="n"/>
       <c r="J277" s="37" t="n"/>
+      <c r="K277" s="36" t="n"/>
     </row>
     <row r="278" ht="28" customHeight="1">
       <c r="A278" s="36" t="n"/>
@@ -21240,6 +21830,7 @@
       <c r="H278" s="39" t="n"/>
       <c r="I278" s="38" t="n"/>
       <c r="J278" s="37" t="n"/>
+      <c r="K278" s="36" t="n"/>
     </row>
     <row r="279" ht="28" customHeight="1">
       <c r="A279" s="36" t="n"/>
@@ -21252,6 +21843,7 @@
       <c r="H279" s="39" t="n"/>
       <c r="I279" s="38" t="n"/>
       <c r="J279" s="37" t="n"/>
+      <c r="K279" s="36" t="n"/>
     </row>
     <row r="280" ht="28" customHeight="1">
       <c r="A280" s="36" t="n"/>
@@ -21264,6 +21856,7 @@
       <c r="H280" s="39" t="n"/>
       <c r="I280" s="38" t="n"/>
       <c r="J280" s="37" t="n"/>
+      <c r="K280" s="36" t="n"/>
     </row>
     <row r="281" ht="28" customHeight="1">
       <c r="A281" s="36" t="n"/>
@@ -21276,6 +21869,7 @@
       <c r="H281" s="39" t="n"/>
       <c r="I281" s="38" t="n"/>
       <c r="J281" s="37" t="n"/>
+      <c r="K281" s="36" t="n"/>
     </row>
     <row r="282" ht="28" customHeight="1">
       <c r="A282" s="36" t="n"/>
@@ -21288,6 +21882,7 @@
       <c r="H282" s="39" t="n"/>
       <c r="I282" s="38" t="n"/>
       <c r="J282" s="37" t="n"/>
+      <c r="K282" s="36" t="n"/>
     </row>
     <row r="283" ht="28" customHeight="1">
       <c r="A283" s="36" t="n"/>
@@ -21300,6 +21895,7 @@
       <c r="H283" s="39" t="n"/>
       <c r="I283" s="38" t="n"/>
       <c r="J283" s="37" t="n"/>
+      <c r="K283" s="36" t="n"/>
     </row>
     <row r="284" ht="28" customHeight="1">
       <c r="A284" s="36" t="n"/>
@@ -21312,6 +21908,7 @@
       <c r="H284" s="39" t="n"/>
       <c r="I284" s="38" t="n"/>
       <c r="J284" s="37" t="n"/>
+      <c r="K284" s="36" t="n"/>
     </row>
     <row r="285" ht="28" customHeight="1">
       <c r="A285" s="36" t="n"/>
@@ -21324,6 +21921,7 @@
       <c r="H285" s="39" t="n"/>
       <c r="I285" s="38" t="n"/>
       <c r="J285" s="37" t="n"/>
+      <c r="K285" s="36" t="n"/>
     </row>
     <row r="286" ht="28" customHeight="1">
       <c r="A286" s="36" t="n"/>
@@ -21336,6 +21934,7 @@
       <c r="H286" s="39" t="n"/>
       <c r="I286" s="38" t="n"/>
       <c r="J286" s="37" t="n"/>
+      <c r="K286" s="36" t="n"/>
     </row>
     <row r="287" ht="28" customHeight="1">
       <c r="A287" s="36" t="n"/>
@@ -21348,6 +21947,7 @@
       <c r="H287" s="39" t="n"/>
       <c r="I287" s="38" t="n"/>
       <c r="J287" s="37" t="n"/>
+      <c r="K287" s="36" t="n"/>
     </row>
     <row r="288" ht="28" customHeight="1">
       <c r="A288" s="36" t="n"/>
@@ -21360,6 +21960,7 @@
       <c r="H288" s="39" t="n"/>
       <c r="I288" s="38" t="n"/>
       <c r="J288" s="37" t="n"/>
+      <c r="K288" s="36" t="n"/>
     </row>
     <row r="289" ht="28" customHeight="1">
       <c r="A289" s="36" t="n"/>
@@ -21372,6 +21973,7 @@
       <c r="H289" s="39" t="n"/>
       <c r="I289" s="38" t="n"/>
       <c r="J289" s="37" t="n"/>
+      <c r="K289" s="36" t="n"/>
     </row>
     <row r="290" ht="28" customHeight="1">
       <c r="A290" s="36" t="n"/>
@@ -21384,6 +21986,7 @@
       <c r="H290" s="39" t="n"/>
       <c r="I290" s="38" t="n"/>
       <c r="J290" s="37" t="n"/>
+      <c r="K290" s="36" t="n"/>
     </row>
     <row r="291" ht="28" customHeight="1">
       <c r="A291" s="36" t="n"/>
@@ -21396,6 +21999,7 @@
       <c r="H291" s="39" t="n"/>
       <c r="I291" s="38" t="n"/>
       <c r="J291" s="37" t="n"/>
+      <c r="K291" s="36" t="n"/>
     </row>
     <row r="292" ht="28" customHeight="1">
       <c r="A292" s="36" t="n"/>
@@ -21408,6 +22012,7 @@
       <c r="H292" s="39" t="n"/>
       <c r="I292" s="38" t="n"/>
       <c r="J292" s="37" t="n"/>
+      <c r="K292" s="36" t="n"/>
     </row>
     <row r="293" ht="28" customHeight="1">
       <c r="A293" s="36" t="n"/>
@@ -21420,6 +22025,7 @@
       <c r="H293" s="39" t="n"/>
       <c r="I293" s="38" t="n"/>
       <c r="J293" s="37" t="n"/>
+      <c r="K293" s="36" t="n"/>
     </row>
     <row r="294" ht="28" customHeight="1">
       <c r="A294" s="36" t="n"/>
@@ -21432,6 +22038,7 @@
       <c r="H294" s="39" t="n"/>
       <c r="I294" s="38" t="n"/>
       <c r="J294" s="37" t="n"/>
+      <c r="K294" s="36" t="n"/>
     </row>
     <row r="295" ht="28" customHeight="1">
       <c r="A295" s="36" t="n"/>
@@ -21444,6 +22051,7 @@
       <c r="H295" s="39" t="n"/>
       <c r="I295" s="38" t="n"/>
       <c r="J295" s="37" t="n"/>
+      <c r="K295" s="36" t="n"/>
     </row>
     <row r="296" ht="28" customHeight="1">
       <c r="A296" s="36" t="n"/>
@@ -21456,6 +22064,7 @@
       <c r="H296" s="39" t="n"/>
       <c r="I296" s="38" t="n"/>
       <c r="J296" s="37" t="n"/>
+      <c r="K296" s="36" t="n"/>
     </row>
     <row r="297" ht="28" customHeight="1">
       <c r="A297" s="36" t="n"/>
@@ -21468,6 +22077,7 @@
       <c r="H297" s="39" t="n"/>
       <c r="I297" s="38" t="n"/>
       <c r="J297" s="37" t="n"/>
+      <c r="K297" s="36" t="n"/>
     </row>
     <row r="298" ht="28" customHeight="1">
       <c r="A298" s="36" t="n"/>
@@ -21480,6 +22090,7 @@
       <c r="H298" s="39" t="n"/>
       <c r="I298" s="38" t="n"/>
       <c r="J298" s="37" t="n"/>
+      <c r="K298" s="36" t="n"/>
     </row>
     <row r="299" ht="28" customHeight="1">
       <c r="A299" s="36" t="n"/>
@@ -21492,6 +22103,7 @@
       <c r="H299" s="39" t="n"/>
       <c r="I299" s="38" t="n"/>
       <c r="J299" s="37" t="n"/>
+      <c r="K299" s="36" t="n"/>
     </row>
     <row r="300" ht="28" customHeight="1">
       <c r="A300" s="36" t="n"/>
@@ -21504,6 +22116,7 @@
       <c r="H300" s="39" t="n"/>
       <c r="I300" s="38" t="n"/>
       <c r="J300" s="37" t="n"/>
+      <c r="K300" s="36" t="n"/>
     </row>
     <row r="301" ht="28" customHeight="1">
       <c r="A301" s="36" t="n"/>
@@ -21516,6 +22129,7 @@
       <c r="H301" s="39" t="n"/>
       <c r="I301" s="38" t="n"/>
       <c r="J301" s="37" t="n"/>
+      <c r="K301" s="36" t="n"/>
     </row>
     <row r="302" ht="28" customHeight="1">
       <c r="A302" s="36" t="n"/>
@@ -21528,6 +22142,7 @@
       <c r="H302" s="39" t="n"/>
       <c r="I302" s="38" t="n"/>
       <c r="J302" s="37" t="n"/>
+      <c r="K302" s="36" t="n"/>
     </row>
     <row r="303" ht="28" customHeight="1">
       <c r="A303" s="36" t="n"/>
@@ -21540,9 +22155,10 @@
       <c r="H303" s="39" t="n"/>
       <c r="I303" s="38" t="n"/>
       <c r="J303" s="37" t="n"/>
+      <c r="K303" s="36" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J303"/>
+  <autoFilter ref="A3:K303"/>
   <conditionalFormatting sqref="G4:G303">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="3">
       <formula>"نشط"</formula>
@@ -21551,7 +22167,7 @@
       <formula>"موقوف"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:J303">
+  <conditionalFormatting sqref="A4:K303">
     <cfRule type="expression" priority="3" dxfId="2">
       <formula>AND(MOD(ROW(),2)=1,$A4&lt;&gt;"")</formula>
     </cfRule>
